--- a/data/stocks_20260403_165405.xlsx
+++ b/data/stocks_20260403_165405.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T72"/>
+  <dimension ref="A1:T70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,10 +519,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>000858</t>
-        </is>
+      <c r="A2" t="n">
+        <v>858</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -585,10 +583,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="A3" t="n">
+        <v>300750</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -651,10 +647,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>600030</t>
-        </is>
+      <c r="A4" t="n">
+        <v>600030</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -717,10 +711,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>600118</t>
-        </is>
+      <c r="A5" t="n">
+        <v>600118</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -783,10 +775,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="A6" t="n">
+        <v>300308</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -849,10 +839,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>601398</t>
-        </is>
+      <c r="A7" t="n">
+        <v>601398</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -915,10 +903,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>601919</t>
-        </is>
+      <c r="A8" t="n">
+        <v>601919</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -981,10 +967,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>002261</t>
-        </is>
+      <c r="A9" t="n">
+        <v>2261</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1047,10 +1031,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="A10" t="n">
+        <v>688041</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1113,10 +1095,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="A11" t="n">
+        <v>300502</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,10 +1159,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="A12" t="n">
+        <v>300394</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1245,10 +1223,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="A13" t="n">
+        <v>988</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1311,10 +1287,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>603986</t>
-        </is>
+      <c r="A14" t="n">
+        <v>603986</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1377,10 +1351,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>688525</t>
-        </is>
+      <c r="A15" t="n">
+        <v>688525</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1443,10 +1415,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>300042</t>
-        </is>
+      <c r="A16" t="n">
+        <v>300042</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1509,10 +1479,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>300302</t>
-        </is>
+      <c r="A17" t="n">
+        <v>300302</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1575,10 +1543,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>000020</t>
-        </is>
+      <c r="A18" t="n">
+        <v>20</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1641,10 +1607,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>603881</t>
-        </is>
+      <c r="A19" t="n">
+        <v>603881</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1707,10 +1671,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>300017</t>
-        </is>
+      <c r="A20" t="n">
+        <v>300017</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1773,10 +1735,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>300418</t>
-        </is>
+      <c r="A21" t="n">
+        <v>300418</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1839,10 +1799,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>002230</t>
-        </is>
+      <c r="A22" t="n">
+        <v>2230</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1905,10 +1863,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>300058</t>
-        </is>
+      <c r="A23" t="n">
+        <v>300058</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1971,10 +1927,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>300496</t>
-        </is>
+      <c r="A24" t="n">
+        <v>300496</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2037,10 +1991,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>000547</t>
-        </is>
+      <c r="A25" t="n">
+        <v>547</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2103,10 +2055,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>002202</t>
-        </is>
+      <c r="A26" t="n">
+        <v>2202</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2169,10 +2119,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>301128</t>
-        </is>
+      <c r="A27" t="n">
+        <v>301128</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2235,10 +2183,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>601899</t>
-        </is>
+      <c r="A28" t="n">
+        <v>601899</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2301,10 +2247,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>600219</t>
-        </is>
+      <c r="A29" t="n">
+        <v>600219</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2367,10 +2311,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>601939</t>
-        </is>
+      <c r="A30" t="n">
+        <v>601939</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2433,10 +2375,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>600048</t>
-        </is>
+      <c r="A31" t="n">
+        <v>600048</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2499,10 +2439,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>600941</t>
-        </is>
+      <c r="A32" t="n">
+        <v>600941</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2565,10 +2503,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>002352</t>
-        </is>
+      <c r="A33" t="n">
+        <v>2352</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2631,10 +2567,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>603803</t>
-        </is>
+      <c r="A34" t="n">
+        <v>603803</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2697,10 +2631,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>002624</t>
-        </is>
+      <c r="A35" t="n">
+        <v>2624</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2763,10 +2695,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>002558</t>
-        </is>
+      <c r="A36" t="n">
+        <v>2558</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2829,10 +2759,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>601088</t>
-        </is>
+      <c r="A37" t="n">
+        <v>601088</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2895,10 +2823,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>600963</t>
-        </is>
+      <c r="A38" t="n">
+        <v>600963</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2961,10 +2887,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>601877</t>
-        </is>
+      <c r="A39" t="n">
+        <v>601877</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3027,10 +2951,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>002049</t>
-        </is>
+      <c r="A40" t="n">
+        <v>2049</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3093,10 +3015,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>688271</t>
-        </is>
+      <c r="A41" t="n">
+        <v>688271</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3159,10 +3079,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>688608</t>
-        </is>
+      <c r="A42" t="n">
+        <v>688608</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3225,10 +3143,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>688099</t>
-        </is>
+      <c r="A43" t="n">
+        <v>688099</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3291,63 +3207,61 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>688521</t>
-        </is>
+      <c r="A44" t="n">
+        <v>688332</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>芯原股份</t>
+          <t>中科蓝讯</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>224.8</v>
+        <v>118.96</v>
       </c>
       <c r="D44" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>216.28</v>
+        <v>118.33</v>
       </c>
       <c r="F44" t="n">
-        <v>212.15</v>
+        <v>116.27</v>
       </c>
       <c r="G44" t="n">
-        <v>212.91</v>
+        <v>120.7</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.242</v>
+        <v>-3.856</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.687</v>
+        <v>-4.536</v>
       </c>
       <c r="J44" t="n">
-        <v>78.33</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>69.73</v>
+        <v>51.98</v>
       </c>
       <c r="L44" t="n">
-        <v>95.55</v>
+        <v>99.31</v>
       </c>
       <c r="M44" t="n">
-        <v>1801.45</v>
+        <v>117.24</v>
       </c>
       <c r="N44" t="n">
-        <v>1830.84</v>
+        <v>129.17</v>
       </c>
       <c r="O44" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="P44" t="n">
-        <v>224</v>
+        <v>119.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>228.97</v>
+        <v>120.5</v>
       </c>
       <c r="R44" t="n">
-        <v>217.96</v>
+        <v>118.2</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
@@ -3357,63 +3271,61 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>688332</t>
-        </is>
+      <c r="A45" t="n">
+        <v>688049</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>中科蓝讯</t>
+          <t>炬芯科技</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>118.96</v>
+        <v>43.63</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="E45" t="n">
-        <v>118.33</v>
+        <v>44.37</v>
       </c>
       <c r="F45" t="n">
-        <v>116.27</v>
+        <v>44.56</v>
       </c>
       <c r="G45" t="n">
-        <v>120.7</v>
+        <v>46.94</v>
       </c>
       <c r="H45" t="n">
-        <v>-3.856</v>
+        <v>-2.146</v>
       </c>
       <c r="I45" t="n">
-        <v>-4.536</v>
+        <v>-2.072</v>
       </c>
       <c r="J45" t="n">
-        <v>67.76000000000001</v>
+        <v>25.14</v>
       </c>
       <c r="K45" t="n">
-        <v>51.98</v>
+        <v>26.87</v>
       </c>
       <c r="L45" t="n">
-        <v>99.31</v>
+        <v>21.68</v>
       </c>
       <c r="M45" t="n">
-        <v>117.24</v>
+        <v>241.16</v>
       </c>
       <c r="N45" t="n">
-        <v>129.17</v>
+        <v>422.9</v>
       </c>
       <c r="O45" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="P45" t="n">
-        <v>119.5</v>
+        <v>43.97</v>
       </c>
       <c r="Q45" t="n">
-        <v>120.5</v>
+        <v>44.19</v>
       </c>
       <c r="R45" t="n">
-        <v>118.2</v>
+        <v>43.56</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
@@ -3423,63 +3335,61 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>688049</t>
-        </is>
+      <c r="A46" t="n">
+        <v>601689</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>炬芯科技</t>
+          <t>拓普集团</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>43.63</v>
+        <v>57.65</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.11</v>
+        <v>-1.72</v>
       </c>
       <c r="E46" t="n">
-        <v>44.37</v>
+        <v>57.84</v>
       </c>
       <c r="F46" t="n">
-        <v>44.56</v>
+        <v>57.71</v>
       </c>
       <c r="G46" t="n">
-        <v>46.94</v>
+        <v>60.06</v>
       </c>
       <c r="H46" t="n">
-        <v>-2.146</v>
+        <v>-2.665</v>
       </c>
       <c r="I46" t="n">
-        <v>-2.072</v>
+        <v>-2.951</v>
       </c>
       <c r="J46" t="n">
-        <v>25.14</v>
+        <v>48.56</v>
       </c>
       <c r="K46" t="n">
-        <v>26.87</v>
+        <v>40.8</v>
       </c>
       <c r="L46" t="n">
-        <v>21.68</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>241.16</v>
+        <v>1625.78</v>
       </c>
       <c r="N46" t="n">
-        <v>422.9</v>
+        <v>2247.79</v>
       </c>
       <c r="O46" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="P46" t="n">
-        <v>43.97</v>
+        <v>59.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>44.19</v>
+        <v>59.29</v>
       </c>
       <c r="R46" t="n">
-        <v>43.56</v>
+        <v>57.33</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
@@ -3489,63 +3399,61 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>601689</t>
-        </is>
+      <c r="A47" t="n">
+        <v>2050</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>拓普集团</t>
+          <t>三花智控</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>57.65</v>
+        <v>41.9</v>
       </c>
       <c r="D47" t="n">
-        <v>-1.72</v>
+        <v>-2.13</v>
       </c>
       <c r="E47" t="n">
-        <v>57.84</v>
+        <v>42.77</v>
       </c>
       <c r="F47" t="n">
-        <v>57.71</v>
+        <v>43.01</v>
       </c>
       <c r="G47" t="n">
-        <v>60.06</v>
+        <v>44.9</v>
       </c>
       <c r="H47" t="n">
-        <v>-2.665</v>
+        <v>-1.893</v>
       </c>
       <c r="I47" t="n">
-        <v>-2.951</v>
+        <v>-1.864</v>
       </c>
       <c r="J47" t="n">
-        <v>48.56</v>
+        <v>34.07</v>
       </c>
       <c r="K47" t="n">
-        <v>40.8</v>
+        <v>34.88</v>
       </c>
       <c r="L47" t="n">
-        <v>64.06999999999999</v>
+        <v>32.45</v>
       </c>
       <c r="M47" t="n">
-        <v>1625.78</v>
+        <v>4568.37</v>
       </c>
       <c r="N47" t="n">
-        <v>2247.79</v>
+        <v>7288.17</v>
       </c>
       <c r="O47" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="P47" t="n">
-        <v>59.2</v>
+        <v>43</v>
       </c>
       <c r="Q47" t="n">
-        <v>59.29</v>
+        <v>43.42</v>
       </c>
       <c r="R47" t="n">
-        <v>57.33</v>
+        <v>41.88</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
@@ -3555,63 +3463,61 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>002050</t>
-        </is>
+      <c r="A48" t="n">
+        <v>887</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>三花智控</t>
+          <t>中鼎股份</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>41.9</v>
+        <v>17.59</v>
       </c>
       <c r="D48" t="n">
-        <v>-2.13</v>
+        <v>-1.46</v>
       </c>
       <c r="E48" t="n">
-        <v>42.77</v>
+        <v>17.97</v>
       </c>
       <c r="F48" t="n">
-        <v>43.01</v>
+        <v>17.95</v>
       </c>
       <c r="G48" t="n">
-        <v>44.9</v>
+        <v>18.6</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.893</v>
+        <v>-0.734</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.864</v>
+        <v>-0.761</v>
       </c>
       <c r="J48" t="n">
-        <v>34.07</v>
+        <v>41.44</v>
       </c>
       <c r="K48" t="n">
-        <v>34.88</v>
+        <v>40.15</v>
       </c>
       <c r="L48" t="n">
-        <v>32.45</v>
+        <v>44</v>
       </c>
       <c r="M48" t="n">
-        <v>4568.37</v>
+        <v>916.3099999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>7288.17</v>
+        <v>1735.63</v>
       </c>
       <c r="O48" t="n">
-        <v>0.63</v>
+        <v>0.53</v>
       </c>
       <c r="P48" t="n">
-        <v>43</v>
+        <v>17.91</v>
       </c>
       <c r="Q48" t="n">
-        <v>43.42</v>
+        <v>18</v>
       </c>
       <c r="R48" t="n">
-        <v>41.88</v>
+        <v>17.57</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
@@ -3621,63 +3527,61 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>000887</t>
-        </is>
+      <c r="A49" t="n">
+        <v>603236</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>中鼎股份</t>
+          <t>移远通信</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>17.59</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.46</v>
+        <v>1.6</v>
       </c>
       <c r="E49" t="n">
-        <v>17.97</v>
+        <v>73.47</v>
       </c>
       <c r="F49" t="n">
-        <v>17.95</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>18.6</v>
+        <v>76.31</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.734</v>
+        <v>-3.109</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.761</v>
+        <v>-3.342</v>
       </c>
       <c r="J49" t="n">
-        <v>41.44</v>
+        <v>37.82</v>
       </c>
       <c r="K49" t="n">
-        <v>40.15</v>
+        <v>31.01</v>
       </c>
       <c r="L49" t="n">
-        <v>44</v>
+        <v>51.44</v>
       </c>
       <c r="M49" t="n">
-        <v>916.3099999999999</v>
+        <v>520.21</v>
       </c>
       <c r="N49" t="n">
-        <v>1735.63</v>
+        <v>499.08</v>
       </c>
       <c r="O49" t="n">
-        <v>0.53</v>
+        <v>1.04</v>
       </c>
       <c r="P49" t="n">
-        <v>17.91</v>
+        <v>72.33</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>74.81</v>
       </c>
       <c r="R49" t="n">
-        <v>17.57</v>
+        <v>72</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
@@ -3687,63 +3591,61 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>603236</t>
-        </is>
+      <c r="A50" t="n">
+        <v>603072</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>天和磁材</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>73.48999999999999</v>
+        <v>35.14</v>
       </c>
       <c r="D50" t="n">
-        <v>1.6</v>
+        <v>-1.68</v>
       </c>
       <c r="E50" t="n">
-        <v>73.47</v>
+        <v>35.82</v>
       </c>
       <c r="F50" t="n">
-        <v>73.43000000000001</v>
+        <v>35.63</v>
       </c>
       <c r="G50" t="n">
-        <v>76.31</v>
+        <v>37.65</v>
       </c>
       <c r="H50" t="n">
-        <v>-3.109</v>
+        <v>-1.698</v>
       </c>
       <c r="I50" t="n">
-        <v>-3.342</v>
+        <v>-1.663</v>
       </c>
       <c r="J50" t="n">
-        <v>37.82</v>
+        <v>45.89</v>
       </c>
       <c r="K50" t="n">
-        <v>31.01</v>
+        <v>39.7</v>
       </c>
       <c r="L50" t="n">
-        <v>51.44</v>
+        <v>58.28</v>
       </c>
       <c r="M50" t="n">
-        <v>520.21</v>
+        <v>139.61</v>
       </c>
       <c r="N50" t="n">
-        <v>499.08</v>
+        <v>234.48</v>
       </c>
       <c r="O50" t="n">
-        <v>1.04</v>
+        <v>0.6</v>
       </c>
       <c r="P50" t="n">
-        <v>72.33</v>
+        <v>35.74</v>
       </c>
       <c r="Q50" t="n">
-        <v>74.81</v>
+        <v>35.95</v>
       </c>
       <c r="R50" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
@@ -3753,63 +3655,61 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>603072</t>
-        </is>
+      <c r="A51" t="n">
+        <v>301023</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>天和磁材</t>
+          <t>奕帆传动</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>35.14</v>
+        <v>37.1</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.68</v>
+        <v>-2.52</v>
       </c>
       <c r="E51" t="n">
-        <v>35.82</v>
+        <v>38.35</v>
       </c>
       <c r="F51" t="n">
-        <v>35.63</v>
+        <v>38.6</v>
       </c>
       <c r="G51" t="n">
-        <v>37.65</v>
+        <v>40.79</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.698</v>
+        <v>-1.848</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.663</v>
+        <v>-1.682</v>
       </c>
       <c r="J51" t="n">
-        <v>45.89</v>
+        <v>16.9</v>
       </c>
       <c r="K51" t="n">
-        <v>39.7</v>
+        <v>21.12</v>
       </c>
       <c r="L51" t="n">
-        <v>58.28</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>139.61</v>
+        <v>93.61</v>
       </c>
       <c r="N51" t="n">
-        <v>234.48</v>
+        <v>126.36</v>
       </c>
       <c r="O51" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="P51" t="n">
-        <v>35.74</v>
+        <v>38.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>35.95</v>
+        <v>38.45</v>
       </c>
       <c r="R51" t="n">
-        <v>35</v>
+        <v>37.02</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
@@ -3819,63 +3719,61 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>301023</t>
-        </is>
+      <c r="A52" t="n">
+        <v>2074</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>奕帆传动</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37.1</v>
+        <v>33.46</v>
       </c>
       <c r="D52" t="n">
-        <v>-2.52</v>
+        <v>-3.85</v>
       </c>
       <c r="E52" t="n">
-        <v>38.35</v>
+        <v>35.38</v>
       </c>
       <c r="F52" t="n">
-        <v>38.6</v>
+        <v>36.28</v>
       </c>
       <c r="G52" t="n">
-        <v>40.79</v>
+        <v>37.17</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.848</v>
+        <v>-0.754</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.682</v>
+        <v>-0.404</v>
       </c>
       <c r="J52" t="n">
-        <v>16.9</v>
+        <v>16.17</v>
       </c>
       <c r="K52" t="n">
-        <v>21.12</v>
+        <v>29.45</v>
       </c>
       <c r="L52" t="n">
-        <v>8.470000000000001</v>
+        <v>-10.39</v>
       </c>
       <c r="M52" t="n">
-        <v>93.61</v>
+        <v>3053.28</v>
       </c>
       <c r="N52" t="n">
-        <v>126.36</v>
+        <v>4395.15</v>
       </c>
       <c r="O52" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P52" t="n">
-        <v>38.2</v>
+        <v>34.73</v>
       </c>
       <c r="Q52" t="n">
-        <v>38.45</v>
+        <v>35.08</v>
       </c>
       <c r="R52" t="n">
-        <v>37.02</v>
+        <v>33.45</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
@@ -3885,63 +3783,61 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>002074</t>
-        </is>
+      <c r="A53" t="n">
+        <v>300450</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>先导智能</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>33.46</v>
+        <v>46.35</v>
       </c>
       <c r="D53" t="n">
-        <v>-3.85</v>
+        <v>-1.78</v>
       </c>
       <c r="E53" t="n">
-        <v>35.38</v>
+        <v>47.83</v>
       </c>
       <c r="F53" t="n">
-        <v>36.28</v>
+        <v>47.96</v>
       </c>
       <c r="G53" t="n">
-        <v>37.17</v>
+        <v>49.22</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.754</v>
+        <v>-1.578</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.404</v>
+        <v>-1.572</v>
       </c>
       <c r="J53" t="n">
-        <v>16.17</v>
+        <v>35.39</v>
       </c>
       <c r="K53" t="n">
-        <v>29.45</v>
+        <v>40.73</v>
       </c>
       <c r="L53" t="n">
-        <v>-10.39</v>
+        <v>24.71</v>
       </c>
       <c r="M53" t="n">
-        <v>3053.28</v>
+        <v>2518.06</v>
       </c>
       <c r="N53" t="n">
-        <v>4395.15</v>
+        <v>4560.04</v>
       </c>
       <c r="O53" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="P53" t="n">
-        <v>34.73</v>
+        <v>47.32</v>
       </c>
       <c r="Q53" t="n">
-        <v>35.08</v>
+        <v>47.66</v>
       </c>
       <c r="R53" t="n">
-        <v>33.45</v>
+        <v>46.27</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr">
@@ -3951,63 +3847,61 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>300450</t>
-        </is>
+      <c r="A54" t="n">
+        <v>688778</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>先导智能</t>
+          <t>厦钨新能</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>46.35</v>
+        <v>69.16</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.78</v>
+        <v>-2.04</v>
       </c>
       <c r="E54" t="n">
-        <v>47.83</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>47.96</v>
+        <v>72.02</v>
       </c>
       <c r="G54" t="n">
-        <v>49.22</v>
+        <v>73.66</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.578</v>
+        <v>-2.47</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.572</v>
+        <v>-2.484</v>
       </c>
       <c r="J54" t="n">
-        <v>35.39</v>
+        <v>45.76</v>
       </c>
       <c r="K54" t="n">
-        <v>40.73</v>
+        <v>51.6</v>
       </c>
       <c r="L54" t="n">
-        <v>24.71</v>
+        <v>34.07</v>
       </c>
       <c r="M54" t="n">
-        <v>2518.06</v>
+        <v>309.14</v>
       </c>
       <c r="N54" t="n">
-        <v>4560.04</v>
+        <v>536.33</v>
       </c>
       <c r="O54" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="P54" t="n">
-        <v>47.32</v>
+        <v>70.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>47.66</v>
+        <v>71.48</v>
       </c>
       <c r="R54" t="n">
-        <v>46.27</v>
+        <v>68.8</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
@@ -4017,63 +3911,61 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>688778</t>
-        </is>
+      <c r="A55" t="n">
+        <v>688116</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>天奈科技</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>69.16</v>
+        <v>36.9</v>
       </c>
       <c r="D55" t="n">
-        <v>-2.04</v>
+        <v>-2.77</v>
       </c>
       <c r="E55" t="n">
-        <v>71.73999999999999</v>
+        <v>39.03</v>
       </c>
       <c r="F55" t="n">
-        <v>72.02</v>
+        <v>39.82</v>
       </c>
       <c r="G55" t="n">
-        <v>73.66</v>
+        <v>41.36</v>
       </c>
       <c r="H55" t="n">
-        <v>-2.47</v>
+        <v>-1.742</v>
       </c>
       <c r="I55" t="n">
-        <v>-2.484</v>
+        <v>-1.49</v>
       </c>
       <c r="J55" t="n">
-        <v>45.76</v>
+        <v>18.01</v>
       </c>
       <c r="K55" t="n">
-        <v>51.6</v>
+        <v>26.63</v>
       </c>
       <c r="L55" t="n">
-        <v>34.07</v>
+        <v>0.79</v>
       </c>
       <c r="M55" t="n">
-        <v>309.14</v>
+        <v>572.42</v>
       </c>
       <c r="N55" t="n">
-        <v>536.33</v>
+        <v>779.28</v>
       </c>
       <c r="O55" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="P55" t="n">
-        <v>70.8</v>
+        <v>38</v>
       </c>
       <c r="Q55" t="n">
-        <v>71.48</v>
+        <v>38.47</v>
       </c>
       <c r="R55" t="n">
-        <v>68.8</v>
+        <v>36.82</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
@@ -4083,63 +3975,61 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>688116</t>
-        </is>
+      <c r="A56" t="n">
+        <v>603200</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>天奈科技</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>36.9</v>
+        <v>56.21</v>
       </c>
       <c r="D56" t="n">
-        <v>-2.77</v>
+        <v>-2.09</v>
       </c>
       <c r="E56" t="n">
-        <v>39.03</v>
+        <v>57.8</v>
       </c>
       <c r="F56" t="n">
-        <v>39.82</v>
+        <v>57.79</v>
       </c>
       <c r="G56" t="n">
-        <v>41.36</v>
+        <v>62.48</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.742</v>
+        <v>-4.757</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.49</v>
+        <v>-4.806</v>
       </c>
       <c r="J56" t="n">
-        <v>18.01</v>
+        <v>31.53</v>
       </c>
       <c r="K56" t="n">
-        <v>26.63</v>
+        <v>29.17</v>
       </c>
       <c r="L56" t="n">
-        <v>0.79</v>
+        <v>36.25</v>
       </c>
       <c r="M56" t="n">
-        <v>572.42</v>
+        <v>289.85</v>
       </c>
       <c r="N56" t="n">
-        <v>779.28</v>
+        <v>500.34</v>
       </c>
       <c r="O56" t="n">
-        <v>0.73</v>
+        <v>0.58</v>
       </c>
       <c r="P56" t="n">
-        <v>38</v>
+        <v>57.41</v>
       </c>
       <c r="Q56" t="n">
-        <v>38.47</v>
+        <v>58.5</v>
       </c>
       <c r="R56" t="n">
-        <v>36.82</v>
+        <v>56.21</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
@@ -4149,63 +4039,61 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>603200</t>
-        </is>
+      <c r="A57" t="n">
+        <v>300409</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>道氏技术</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>56.21</v>
+        <v>24.02</v>
       </c>
       <c r="D57" t="n">
-        <v>-2.09</v>
+        <v>-1.92</v>
       </c>
       <c r="E57" t="n">
-        <v>57.8</v>
+        <v>24.72</v>
       </c>
       <c r="F57" t="n">
-        <v>57.79</v>
+        <v>24.72</v>
       </c>
       <c r="G57" t="n">
-        <v>62.48</v>
+        <v>26.51</v>
       </c>
       <c r="H57" t="n">
-        <v>-4.757</v>
+        <v>-1.127</v>
       </c>
       <c r="I57" t="n">
-        <v>-4.806</v>
+        <v>-0.969</v>
       </c>
       <c r="J57" t="n">
-        <v>31.53</v>
+        <v>25.6</v>
       </c>
       <c r="K57" t="n">
-        <v>29.17</v>
+        <v>26.1</v>
       </c>
       <c r="L57" t="n">
-        <v>36.25</v>
+        <v>24.61</v>
       </c>
       <c r="M57" t="n">
-        <v>289.85</v>
+        <v>1262.04</v>
       </c>
       <c r="N57" t="n">
-        <v>500.34</v>
+        <v>3605.02</v>
       </c>
       <c r="O57" t="n">
-        <v>0.58</v>
+        <v>0.35</v>
       </c>
       <c r="P57" t="n">
-        <v>57.41</v>
+        <v>24.58</v>
       </c>
       <c r="Q57" t="n">
-        <v>58.5</v>
+        <v>24.74</v>
       </c>
       <c r="R57" t="n">
-        <v>56.21</v>
+        <v>24.01</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
@@ -4215,63 +4103,61 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>300409</t>
-        </is>
+      <c r="A58" t="n">
+        <v>2202</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>道氏技术</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>24.02</v>
+        <v>24.22</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.92</v>
+        <v>0.87</v>
       </c>
       <c r="E58" t="n">
-        <v>24.72</v>
+        <v>25.53</v>
       </c>
       <c r="F58" t="n">
-        <v>24.72</v>
+        <v>26.65</v>
       </c>
       <c r="G58" t="n">
-        <v>26.51</v>
+        <v>28.3</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.127</v>
+        <v>-0.67</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.969</v>
+        <v>-0.007</v>
       </c>
       <c r="J58" t="n">
-        <v>25.6</v>
+        <v>12.64</v>
       </c>
       <c r="K58" t="n">
-        <v>26.1</v>
+        <v>13.15</v>
       </c>
       <c r="L58" t="n">
-        <v>24.61</v>
+        <v>11.62</v>
       </c>
       <c r="M58" t="n">
-        <v>1262.04</v>
+        <v>24211.4</v>
       </c>
       <c r="N58" t="n">
-        <v>3605.02</v>
+        <v>28234.59</v>
       </c>
       <c r="O58" t="n">
-        <v>0.35</v>
+        <v>0.86</v>
       </c>
       <c r="P58" t="n">
-        <v>24.58</v>
+        <v>23.9</v>
       </c>
       <c r="Q58" t="n">
-        <v>24.74</v>
+        <v>24.44</v>
       </c>
       <c r="R58" t="n">
-        <v>24.01</v>
+        <v>22.93</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
@@ -4281,63 +4167,61 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>002202</t>
-        </is>
+      <c r="A59" t="n">
+        <v>688066</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>金风科技</t>
+          <t>航天宏图</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>24.22</v>
+        <v>17</v>
       </c>
       <c r="D59" t="n">
-        <v>0.87</v>
+        <v>-6.44</v>
       </c>
       <c r="E59" t="n">
-        <v>25.53</v>
+        <v>18.82</v>
       </c>
       <c r="F59" t="n">
-        <v>26.65</v>
+        <v>19.47</v>
       </c>
       <c r="G59" t="n">
-        <v>28.3</v>
+        <v>21.13</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.67</v>
+        <v>-2.121</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.007</v>
+        <v>-2.019</v>
       </c>
       <c r="J59" t="n">
-        <v>12.64</v>
+        <v>7.11</v>
       </c>
       <c r="K59" t="n">
-        <v>13.15</v>
+        <v>11.26</v>
       </c>
       <c r="L59" t="n">
-        <v>11.62</v>
+        <v>-1.2</v>
       </c>
       <c r="M59" t="n">
-        <v>24211.4</v>
+        <v>1167.25</v>
       </c>
       <c r="N59" t="n">
-        <v>28234.59</v>
+        <v>1032.33</v>
       </c>
       <c r="O59" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="P59" t="n">
-        <v>23.9</v>
+        <v>18.22</v>
       </c>
       <c r="Q59" t="n">
-        <v>24.44</v>
+        <v>18.3</v>
       </c>
       <c r="R59" t="n">
-        <v>22.93</v>
+        <v>16.86</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
@@ -4347,63 +4231,61 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>688066</t>
-        </is>
+      <c r="A60" t="n">
+        <v>600990</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>航天宏图</t>
+          <t>四创电子</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>17</v>
+        <v>21.65</v>
       </c>
       <c r="D60" t="n">
-        <v>-6.44</v>
+        <v>-2.61</v>
       </c>
       <c r="E60" t="n">
-        <v>18.82</v>
+        <v>22.44</v>
       </c>
       <c r="F60" t="n">
-        <v>19.47</v>
+        <v>22.45</v>
       </c>
       <c r="G60" t="n">
-        <v>21.13</v>
+        <v>23.78</v>
       </c>
       <c r="H60" t="n">
-        <v>-2.121</v>
+        <v>-1.238</v>
       </c>
       <c r="I60" t="n">
-        <v>-2.019</v>
+        <v>-1.21</v>
       </c>
       <c r="J60" t="n">
-        <v>7.11</v>
+        <v>20.72</v>
       </c>
       <c r="K60" t="n">
-        <v>11.26</v>
+        <v>24.46</v>
       </c>
       <c r="L60" t="n">
-        <v>-1.2</v>
+        <v>13.24</v>
       </c>
       <c r="M60" t="n">
-        <v>1167.25</v>
+        <v>322.53</v>
       </c>
       <c r="N60" t="n">
-        <v>1032.33</v>
+        <v>416.36</v>
       </c>
       <c r="O60" t="n">
-        <v>1.13</v>
+        <v>0.77</v>
       </c>
       <c r="P60" t="n">
-        <v>18.22</v>
+        <v>22.23</v>
       </c>
       <c r="Q60" t="n">
-        <v>18.3</v>
+        <v>22.34</v>
       </c>
       <c r="R60" t="n">
-        <v>16.86</v>
+        <v>21.56</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
@@ -4413,63 +4295,61 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>600990</t>
-        </is>
+      <c r="A61" t="n">
+        <v>2025</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>四创电子</t>
+          <t>航天电器</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>21.65</v>
+        <v>60.65</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.61</v>
+        <v>0.05</v>
       </c>
       <c r="E61" t="n">
-        <v>22.44</v>
+        <v>63.2</v>
       </c>
       <c r="F61" t="n">
-        <v>22.45</v>
+        <v>63.67</v>
       </c>
       <c r="G61" t="n">
-        <v>23.78</v>
+        <v>60.64</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.238</v>
+        <v>2.365</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.21</v>
+        <v>2.654</v>
       </c>
       <c r="J61" t="n">
-        <v>20.72</v>
+        <v>40.32</v>
       </c>
       <c r="K61" t="n">
-        <v>24.46</v>
+        <v>53.83</v>
       </c>
       <c r="L61" t="n">
-        <v>13.24</v>
+        <v>13.29</v>
       </c>
       <c r="M61" t="n">
-        <v>322.53</v>
+        <v>2381.43</v>
       </c>
       <c r="N61" t="n">
-        <v>416.36</v>
+        <v>3609.08</v>
       </c>
       <c r="O61" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="P61" t="n">
-        <v>22.23</v>
+        <v>60.62</v>
       </c>
       <c r="Q61" t="n">
-        <v>22.34</v>
+        <v>62.83</v>
       </c>
       <c r="R61" t="n">
-        <v>21.56</v>
+        <v>58.7</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
@@ -4479,63 +4359,61 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>002025</t>
-        </is>
+      <c r="A62" t="n">
+        <v>600584</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>航天电器</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>60.65</v>
+        <v>38.29</v>
       </c>
       <c r="D62" t="n">
-        <v>0.05</v>
+        <v>-0.49</v>
       </c>
       <c r="E62" t="n">
-        <v>63.2</v>
+        <v>38.97</v>
       </c>
       <c r="F62" t="n">
-        <v>63.67</v>
+        <v>39.3</v>
       </c>
       <c r="G62" t="n">
-        <v>60.64</v>
+        <v>42.17</v>
       </c>
       <c r="H62" t="n">
-        <v>2.365</v>
+        <v>-1.96</v>
       </c>
       <c r="I62" t="n">
-        <v>2.654</v>
+        <v>-1.593</v>
       </c>
       <c r="J62" t="n">
-        <v>40.32</v>
+        <v>10.7</v>
       </c>
       <c r="K62" t="n">
-        <v>53.83</v>
+        <v>13.23</v>
       </c>
       <c r="L62" t="n">
-        <v>13.29</v>
+        <v>5.65</v>
       </c>
       <c r="M62" t="n">
-        <v>2381.43</v>
+        <v>2617.06</v>
       </c>
       <c r="N62" t="n">
-        <v>3609.08</v>
+        <v>5761.89</v>
       </c>
       <c r="O62" t="n">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="P62" t="n">
-        <v>60.62</v>
+        <v>38.88</v>
       </c>
       <c r="Q62" t="n">
-        <v>62.83</v>
+        <v>38.98</v>
       </c>
       <c r="R62" t="n">
-        <v>58.7</v>
+        <v>38.02</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr">
@@ -4545,63 +4423,61 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>600584</t>
-        </is>
+      <c r="A63" t="n">
+        <v>688295</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>中复神鹰</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>38.29</v>
+        <v>50.01</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.49</v>
+        <v>-3.83</v>
       </c>
       <c r="E63" t="n">
-        <v>38.97</v>
+        <v>53.69</v>
       </c>
       <c r="F63" t="n">
-        <v>39.3</v>
+        <v>56.69</v>
       </c>
       <c r="G63" t="n">
-        <v>42.17</v>
+        <v>51.84</v>
       </c>
       <c r="H63" t="n">
-        <v>-1.96</v>
+        <v>4.683</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.593</v>
+        <v>5.954</v>
       </c>
       <c r="J63" t="n">
-        <v>10.7</v>
+        <v>16.31</v>
       </c>
       <c r="K63" t="n">
-        <v>13.23</v>
+        <v>34.59</v>
       </c>
       <c r="L63" t="n">
-        <v>5.65</v>
+        <v>-20.24</v>
       </c>
       <c r="M63" t="n">
-        <v>2617.06</v>
+        <v>1933.17</v>
       </c>
       <c r="N63" t="n">
-        <v>5761.89</v>
+        <v>2814.68</v>
       </c>
       <c r="O63" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P63" t="n">
-        <v>38.88</v>
+        <v>52.38</v>
       </c>
       <c r="Q63" t="n">
-        <v>38.98</v>
+        <v>52.66</v>
       </c>
       <c r="R63" t="n">
-        <v>38.02</v>
+        <v>50</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr">
@@ -4611,63 +4487,61 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>688295</t>
-        </is>
+      <c r="A64" t="n">
+        <v>300759</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>中复神鹰</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>50.01</v>
+        <v>30.07</v>
       </c>
       <c r="D64" t="n">
-        <v>-3.83</v>
+        <v>-1.8</v>
       </c>
       <c r="E64" t="n">
-        <v>53.69</v>
+        <v>29.16</v>
       </c>
       <c r="F64" t="n">
-        <v>56.69</v>
+        <v>27.49</v>
       </c>
       <c r="G64" t="n">
-        <v>51.84</v>
+        <v>27.46</v>
       </c>
       <c r="H64" t="n">
-        <v>4.683</v>
+        <v>0.153</v>
       </c>
       <c r="I64" t="n">
-        <v>5.954</v>
+        <v>-0.416</v>
       </c>
       <c r="J64" t="n">
-        <v>16.31</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>34.59</v>
+        <v>63.86</v>
       </c>
       <c r="L64" t="n">
-        <v>-20.24</v>
+        <v>108.74</v>
       </c>
       <c r="M64" t="n">
-        <v>1933.17</v>
+        <v>4109.71</v>
       </c>
       <c r="N64" t="n">
-        <v>2814.68</v>
+        <v>3006.3</v>
       </c>
       <c r="O64" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="P64" t="n">
-        <v>52.38</v>
+        <v>30.39</v>
       </c>
       <c r="Q64" t="n">
-        <v>52.66</v>
+        <v>30.59</v>
       </c>
       <c r="R64" t="n">
-        <v>50</v>
+        <v>29.82</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr">
@@ -4678,128 +4552,124 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>920002</v>
+        <v>688621</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>万达轴承</t>
+          <t>阳光诺和</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>84.01000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="D65" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="E65" t="n">
+        <v>66.33</v>
+      </c>
+      <c r="F65" t="n">
+        <v>63.53</v>
+      </c>
+      <c r="G65" t="n">
+        <v>63.03</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-0.494</v>
+      </c>
+      <c r="J65" t="n">
+        <v>77.61</v>
+      </c>
+      <c r="K65" t="n">
+        <v>72.14</v>
+      </c>
+      <c r="L65" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="M65" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>219.18</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P65" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>68</v>
+      </c>
+      <c r="R65" t="n">
+        <v>65</v>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>301333</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>诺思格</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="E66" t="n">
+        <v>67.86</v>
+      </c>
+      <c r="F66" t="n">
+        <v>63.27</v>
+      </c>
+      <c r="G66" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-0.417</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-1.724</v>
+      </c>
+      <c r="J66" t="n">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="K66" t="n">
+        <v>66.17</v>
+      </c>
+      <c r="L66" t="n">
+        <v>80.69</v>
+      </c>
+      <c r="M66" t="n">
+        <v>287.12</v>
+      </c>
+      <c r="N66" t="n">
+        <v>229.26</v>
+      </c>
+      <c r="O66" t="n">
         <v>1.25</v>
       </c>
-      <c r="E65" t="n">
-        <v>82.75</v>
-      </c>
-      <c r="F65" t="n">
-        <v>82.79000000000001</v>
-      </c>
-      <c r="G65" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-3.112</v>
-      </c>
-      <c r="I65" t="n">
-        <v>-3.803</v>
-      </c>
-      <c r="J65" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="K65" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="L65" t="n">
-        <v>71.01000000000001</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="P65" t="n">
-        <v>83</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="R65" t="n">
-        <v>83</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>300759</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>康龙化成</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>30.07</v>
-      </c>
-      <c r="D66" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="E66" t="n">
-        <v>29.16</v>
-      </c>
-      <c r="F66" t="n">
-        <v>27.49</v>
-      </c>
-      <c r="G66" t="n">
-        <v>27.46</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="I66" t="n">
-        <v>-0.416</v>
-      </c>
-      <c r="J66" t="n">
-        <v>78.81999999999999</v>
-      </c>
-      <c r="K66" t="n">
-        <v>63.86</v>
-      </c>
-      <c r="L66" t="n">
-        <v>108.74</v>
-      </c>
-      <c r="M66" t="n">
-        <v>4109.71</v>
-      </c>
-      <c r="N66" t="n">
-        <v>3006.3</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1.37</v>
-      </c>
       <c r="P66" t="n">
-        <v>30.39</v>
+        <v>66.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>30.59</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="R66" t="n">
-        <v>29.82</v>
+        <v>65.41</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr">
@@ -4809,63 +4679,61 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>688621</t>
-        </is>
+      <c r="A67" t="n">
+        <v>963</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>阳光诺和</t>
+          <t>华东医药</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>65.56999999999999</v>
+        <v>36.29</v>
       </c>
       <c r="D67" t="n">
-        <v>-4.68</v>
+        <v>-1.6</v>
       </c>
       <c r="E67" t="n">
-        <v>66.33</v>
+        <v>36.08</v>
       </c>
       <c r="F67" t="n">
-        <v>63.53</v>
+        <v>35.1</v>
       </c>
       <c r="G67" t="n">
-        <v>63.03</v>
+        <v>35.22</v>
       </c>
       <c r="H67" t="n">
-        <v>0.417</v>
+        <v>0.037</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.494</v>
+        <v>-0.264</v>
       </c>
       <c r="J67" t="n">
-        <v>77.61</v>
+        <v>78.05</v>
       </c>
       <c r="K67" t="n">
-        <v>72.14</v>
+        <v>67.72</v>
       </c>
       <c r="L67" t="n">
-        <v>88.56</v>
+        <v>98.69</v>
       </c>
       <c r="M67" t="n">
-        <v>303.1</v>
+        <v>1153.73</v>
       </c>
       <c r="N67" t="n">
-        <v>219.18</v>
+        <v>1076.56</v>
       </c>
       <c r="O67" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="P67" t="n">
-        <v>67.40000000000001</v>
+        <v>36.3</v>
       </c>
       <c r="Q67" t="n">
-        <v>68</v>
+        <v>36.6</v>
       </c>
       <c r="R67" t="n">
-        <v>65</v>
+        <v>36.04</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr">
@@ -4875,63 +4743,61 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>301333</t>
-        </is>
+      <c r="A68" t="n">
+        <v>603658</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>诺思格</t>
+          <t>安图生物</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>65.90000000000001</v>
+        <v>33.98</v>
       </c>
       <c r="D68" t="n">
-        <v>-5.14</v>
+        <v>-1.48</v>
       </c>
       <c r="E68" t="n">
-        <v>67.86</v>
+        <v>33.96</v>
       </c>
       <c r="F68" t="n">
-        <v>63.27</v>
+        <v>33.51</v>
       </c>
       <c r="G68" t="n">
-        <v>63.26</v>
+        <v>34.18</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.417</v>
+        <v>-0.479</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.724</v>
+        <v>-0.603</v>
       </c>
       <c r="J68" t="n">
-        <v>71.01000000000001</v>
+        <v>64.03</v>
       </c>
       <c r="K68" t="n">
-        <v>66.17</v>
+        <v>49.79</v>
       </c>
       <c r="L68" t="n">
-        <v>80.69</v>
+        <v>92.52</v>
       </c>
       <c r="M68" t="n">
-        <v>287.12</v>
+        <v>194.17</v>
       </c>
       <c r="N68" t="n">
-        <v>229.26</v>
+        <v>193.2</v>
       </c>
       <c r="O68" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P68" t="n">
-        <v>66.5</v>
+        <v>34.28</v>
       </c>
       <c r="Q68" t="n">
-        <v>67.31999999999999</v>
+        <v>34.45</v>
       </c>
       <c r="R68" t="n">
-        <v>65.41</v>
+        <v>33.73</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr">
@@ -4941,63 +4807,61 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>000963</t>
-        </is>
+      <c r="A69" t="n">
+        <v>300357</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>华东医药</t>
+          <t>我武生物</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36.29</v>
+        <v>25.53</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.6</v>
+        <v>-3.44</v>
       </c>
       <c r="E69" t="n">
-        <v>36.08</v>
+        <v>25.97</v>
       </c>
       <c r="F69" t="n">
-        <v>35.1</v>
+        <v>25.05</v>
       </c>
       <c r="G69" t="n">
-        <v>35.22</v>
+        <v>25.05</v>
       </c>
       <c r="H69" t="n">
-        <v>0.037</v>
+        <v>-0.186</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.264</v>
+        <v>-0.486</v>
       </c>
       <c r="J69" t="n">
-        <v>78.05</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>67.72</v>
+        <v>66.77</v>
       </c>
       <c r="L69" t="n">
-        <v>98.69</v>
+        <v>88.42</v>
       </c>
       <c r="M69" t="n">
-        <v>1153.73</v>
+        <v>1057.86</v>
       </c>
       <c r="N69" t="n">
-        <v>1076.56</v>
+        <v>1143.81</v>
       </c>
       <c r="O69" t="n">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="P69" t="n">
-        <v>36.3</v>
+        <v>26.07</v>
       </c>
       <c r="Q69" t="n">
-        <v>36.6</v>
+        <v>26.28</v>
       </c>
       <c r="R69" t="n">
-        <v>36.04</v>
+        <v>25.49</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr">
@@ -5007,198 +4871,64 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>603658</t>
-        </is>
+      <c r="A70" t="n">
+        <v>688050</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>安图生物</t>
+          <t>爱博医疗</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>33.98</v>
+        <v>50.9</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.48</v>
+        <v>-1.45</v>
       </c>
       <c r="E70" t="n">
-        <v>33.96</v>
+        <v>51.72</v>
       </c>
       <c r="F70" t="n">
-        <v>33.51</v>
+        <v>51.15</v>
       </c>
       <c r="G70" t="n">
-        <v>34.18</v>
+        <v>53.05</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.479</v>
+        <v>-1.88</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.603</v>
+        <v>-2.032</v>
       </c>
       <c r="J70" t="n">
-        <v>64.03</v>
+        <v>52.2</v>
       </c>
       <c r="K70" t="n">
-        <v>49.79</v>
+        <v>44.88</v>
       </c>
       <c r="L70" t="n">
-        <v>92.52</v>
+        <v>66.83</v>
       </c>
       <c r="M70" t="n">
-        <v>194.17</v>
+        <v>102.26</v>
       </c>
       <c r="N70" t="n">
-        <v>193.2</v>
+        <v>178.13</v>
       </c>
       <c r="O70" t="n">
-        <v>1.01</v>
+        <v>0.57</v>
       </c>
       <c r="P70" t="n">
-        <v>34.28</v>
+        <v>51.55</v>
       </c>
       <c r="Q70" t="n">
-        <v>34.45</v>
+        <v>51.9</v>
       </c>
       <c r="R70" t="n">
-        <v>33.73</v>
+        <v>50.72</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>300357</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>我武生物</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>25.53</v>
-      </c>
-      <c r="D71" t="n">
-        <v>-3.44</v>
-      </c>
-      <c r="E71" t="n">
-        <v>25.97</v>
-      </c>
-      <c r="F71" t="n">
-        <v>25.05</v>
-      </c>
-      <c r="G71" t="n">
-        <v>25.05</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-0.186</v>
-      </c>
-      <c r="I71" t="n">
-        <v>-0.486</v>
-      </c>
-      <c r="J71" t="n">
-        <v>73.98999999999999</v>
-      </c>
-      <c r="K71" t="n">
-        <v>66.77</v>
-      </c>
-      <c r="L71" t="n">
-        <v>88.42</v>
-      </c>
-      <c r="M71" t="n">
-        <v>1057.86</v>
-      </c>
-      <c r="N71" t="n">
-        <v>1143.81</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="P71" t="n">
-        <v>26.07</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>26.28</v>
-      </c>
-      <c r="R71" t="n">
-        <v>25.49</v>
-      </c>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>688050</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>爱博医疗</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="D72" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="E72" t="n">
-        <v>51.72</v>
-      </c>
-      <c r="F72" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="G72" t="n">
-        <v>53.05</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="I72" t="n">
-        <v>-2.032</v>
-      </c>
-      <c r="J72" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="K72" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="L72" t="n">
-        <v>66.83</v>
-      </c>
-      <c r="M72" t="n">
-        <v>102.26</v>
-      </c>
-      <c r="N72" t="n">
-        <v>178.13</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="P72" t="n">
-        <v>51.55</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="R72" t="n">
-        <v>50.72</v>
-      </c>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>

--- a/data/stocks_20260403_165405.xlsx
+++ b/data/stocks_20260403_165405.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股票池" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T70"/>
+  <dimension ref="A1:T57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,60 +1032,60 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>688041</v>
+        <v>300502</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>213.77</v>
+        <v>455.3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.36</v>
+        <v>1.75</v>
       </c>
       <c r="E10" t="n">
-        <v>214.61</v>
+        <v>452.92</v>
       </c>
       <c r="F10" t="n">
-        <v>215.04</v>
+        <v>457.37</v>
       </c>
       <c r="G10" t="n">
-        <v>224.49</v>
+        <v>433.6</v>
       </c>
       <c r="H10" t="n">
-        <v>-8.116</v>
+        <v>16.068</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.98</v>
+        <v>15.984</v>
       </c>
       <c r="J10" t="n">
-        <v>44.24</v>
+        <v>39.56</v>
       </c>
       <c r="K10" t="n">
-        <v>41.41</v>
+        <v>49.58</v>
       </c>
       <c r="L10" t="n">
-        <v>49.89</v>
+        <v>19.52</v>
       </c>
       <c r="M10" t="n">
-        <v>1170.89</v>
+        <v>3363.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1809.41</v>
+        <v>4062.6</v>
       </c>
       <c r="O10" t="n">
-        <v>0.65</v>
+        <v>0.83</v>
       </c>
       <c r="P10" t="n">
-        <v>214.07</v>
+        <v>457</v>
       </c>
       <c r="Q10" t="n">
-        <v>218.17</v>
+        <v>469</v>
       </c>
       <c r="R10" t="n">
-        <v>213.22</v>
+        <v>454.05</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
@@ -1096,60 +1096,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300502</v>
+        <v>300394</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>455.3</v>
+        <v>333.86</v>
       </c>
       <c r="D11" t="n">
-        <v>1.75</v>
+        <v>3.43</v>
       </c>
       <c r="E11" t="n">
-        <v>452.92</v>
+        <v>321.68</v>
       </c>
       <c r="F11" t="n">
-        <v>457.37</v>
+        <v>316.63</v>
       </c>
       <c r="G11" t="n">
-        <v>433.6</v>
+        <v>315.91</v>
       </c>
       <c r="H11" t="n">
-        <v>16.068</v>
+        <v>7.056</v>
       </c>
       <c r="I11" t="n">
-        <v>15.984</v>
+        <v>7.294</v>
       </c>
       <c r="J11" t="n">
-        <v>39.56</v>
+        <v>68.47</v>
       </c>
       <c r="K11" t="n">
-        <v>49.58</v>
+        <v>60.82</v>
       </c>
       <c r="L11" t="n">
-        <v>19.52</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>3363.6</v>
+        <v>3192.38</v>
       </c>
       <c r="N11" t="n">
-        <v>4062.6</v>
+        <v>3427.99</v>
       </c>
       <c r="O11" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="P11" t="n">
-        <v>457</v>
+        <v>337.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>469</v>
+        <v>344.4</v>
       </c>
       <c r="R11" t="n">
-        <v>454.05</v>
+        <v>333.6</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
@@ -1160,60 +1160,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300394</v>
+        <v>988</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>333.86</v>
+        <v>103.54</v>
       </c>
       <c r="D12" t="n">
-        <v>3.43</v>
+        <v>3.19</v>
       </c>
       <c r="E12" t="n">
-        <v>321.68</v>
+        <v>103.81</v>
       </c>
       <c r="F12" t="n">
-        <v>316.63</v>
+        <v>107.5</v>
       </c>
       <c r="G12" t="n">
-        <v>315.91</v>
+        <v>113.89</v>
       </c>
       <c r="H12" t="n">
-        <v>7.056</v>
+        <v>1.573</v>
       </c>
       <c r="I12" t="n">
-        <v>7.294</v>
+        <v>4.361</v>
       </c>
       <c r="J12" t="n">
-        <v>68.47</v>
+        <v>13.63</v>
       </c>
       <c r="K12" t="n">
-        <v>60.82</v>
+        <v>15.71</v>
       </c>
       <c r="L12" t="n">
-        <v>83.76000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>3192.38</v>
+        <v>6851.46</v>
       </c>
       <c r="N12" t="n">
-        <v>3427.99</v>
+        <v>10994.98</v>
       </c>
       <c r="O12" t="n">
-        <v>0.93</v>
+        <v>0.62</v>
       </c>
       <c r="P12" t="n">
-        <v>337.68</v>
+        <v>102.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>344.4</v>
+        <v>105.84</v>
       </c>
       <c r="R12" t="n">
-        <v>333.6</v>
+        <v>101.66</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
@@ -1224,60 +1224,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>988</v>
+        <v>603986</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>兆易创新</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>103.54</v>
+        <v>249.1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.19</v>
+        <v>0.85</v>
       </c>
       <c r="E13" t="n">
-        <v>103.81</v>
+        <v>249.01</v>
       </c>
       <c r="F13" t="n">
-        <v>107.5</v>
+        <v>259.12</v>
       </c>
       <c r="G13" t="n">
-        <v>113.89</v>
+        <v>274.73</v>
       </c>
       <c r="H13" t="n">
-        <v>1.573</v>
+        <v>-10.382</v>
       </c>
       <c r="I13" t="n">
-        <v>4.361</v>
+        <v>-6.275</v>
       </c>
       <c r="J13" t="n">
-        <v>13.63</v>
+        <v>22.01</v>
       </c>
       <c r="K13" t="n">
-        <v>15.71</v>
+        <v>23.2</v>
       </c>
       <c r="L13" t="n">
-        <v>9.460000000000001</v>
+        <v>19.65</v>
       </c>
       <c r="M13" t="n">
-        <v>6851.46</v>
+        <v>1974.72</v>
       </c>
       <c r="N13" t="n">
-        <v>10994.98</v>
+        <v>3027.03</v>
       </c>
       <c r="O13" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="P13" t="n">
-        <v>102.4</v>
+        <v>250.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>105.84</v>
+        <v>254.6</v>
       </c>
       <c r="R13" t="n">
-        <v>101.66</v>
+        <v>247.5</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
@@ -1288,60 +1288,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>603986</v>
+        <v>300042</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>朗科科技</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>249.1</v>
+        <v>41.45</v>
       </c>
       <c r="D14" t="n">
-        <v>0.85</v>
+        <v>-1.8</v>
       </c>
       <c r="E14" t="n">
-        <v>249.01</v>
+        <v>42.55</v>
       </c>
       <c r="F14" t="n">
-        <v>259.12</v>
+        <v>44.62</v>
       </c>
       <c r="G14" t="n">
-        <v>274.73</v>
+        <v>45.26</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.382</v>
+        <v>1.385</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.275</v>
+        <v>2.644</v>
       </c>
       <c r="J14" t="n">
-        <v>22.01</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>23.2</v>
+        <v>18.02</v>
       </c>
       <c r="L14" t="n">
-        <v>19.65</v>
+        <v>-8.9</v>
       </c>
       <c r="M14" t="n">
-        <v>1974.72</v>
+        <v>1392.12</v>
       </c>
       <c r="N14" t="n">
-        <v>3027.03</v>
+        <v>3093.2</v>
       </c>
       <c r="O14" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="P14" t="n">
-        <v>250.99</v>
+        <v>43.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>254.6</v>
+        <v>43.88</v>
       </c>
       <c r="R14" t="n">
-        <v>247.5</v>
+        <v>41.3</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
@@ -1352,60 +1352,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>688525</v>
+        <v>300302</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>同有科技</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>210.29</v>
+        <v>18.68</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.25</v>
+        <v>-3.21</v>
       </c>
       <c r="E15" t="n">
-        <v>216.14</v>
+        <v>19.77</v>
       </c>
       <c r="F15" t="n">
-        <v>226.79</v>
+        <v>20.87</v>
       </c>
       <c r="G15" t="n">
-        <v>226.93</v>
+        <v>21.28</v>
       </c>
       <c r="H15" t="n">
-        <v>8.032</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>13.437</v>
+        <v>0.394</v>
       </c>
       <c r="J15" t="n">
-        <v>14.27</v>
+        <v>5.6</v>
       </c>
       <c r="K15" t="n">
-        <v>29.51</v>
+        <v>14.19</v>
       </c>
       <c r="L15" t="n">
-        <v>-16.22</v>
+        <v>-11.58</v>
       </c>
       <c r="M15" t="n">
-        <v>2148.79</v>
+        <v>1977.02</v>
       </c>
       <c r="N15" t="n">
-        <v>3975.94</v>
+        <v>4187.65</v>
       </c>
       <c r="O15" t="n">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
       <c r="P15" t="n">
-        <v>213.6</v>
+        <v>19.69</v>
       </c>
       <c r="Q15" t="n">
-        <v>217.55</v>
+        <v>19.73</v>
       </c>
       <c r="R15" t="n">
-        <v>210.2</v>
+        <v>18.68</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
@@ -1416,60 +1416,60 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>300042</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>朗科科技</t>
+          <t>深华发A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>41.45</v>
+        <v>14.82</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8</v>
+        <v>-4.2</v>
       </c>
       <c r="E16" t="n">
-        <v>42.55</v>
+        <v>15.72</v>
       </c>
       <c r="F16" t="n">
-        <v>44.62</v>
+        <v>17.03</v>
       </c>
       <c r="G16" t="n">
-        <v>45.26</v>
+        <v>17.02</v>
       </c>
       <c r="H16" t="n">
-        <v>1.385</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>2.644</v>
+        <v>0.547</v>
       </c>
       <c r="J16" t="n">
-        <v>9.050000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="K16" t="n">
-        <v>18.02</v>
+        <v>14.69</v>
       </c>
       <c r="L16" t="n">
-        <v>-8.9</v>
+        <v>-13.17</v>
       </c>
       <c r="M16" t="n">
-        <v>1392.12</v>
+        <v>1059.72</v>
       </c>
       <c r="N16" t="n">
-        <v>3093.2</v>
+        <v>1307.92</v>
       </c>
       <c r="O16" t="n">
-        <v>0.45</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>43.88</v>
+        <v>15.49</v>
       </c>
       <c r="Q16" t="n">
-        <v>43.88</v>
+        <v>15.52</v>
       </c>
       <c r="R16" t="n">
-        <v>41.3</v>
+        <v>14.74</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
@@ -1480,60 +1480,60 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>300302</v>
+        <v>603881</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>数据港</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18.68</v>
+        <v>36.65</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.21</v>
+        <v>0.52</v>
       </c>
       <c r="E17" t="n">
-        <v>19.77</v>
+        <v>37.7</v>
       </c>
       <c r="F17" t="n">
-        <v>20.87</v>
+        <v>37.31</v>
       </c>
       <c r="G17" t="n">
-        <v>21.28</v>
+        <v>37.45</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="I17" t="n">
-        <v>0.394</v>
+        <v>-0.011</v>
       </c>
       <c r="J17" t="n">
-        <v>5.6</v>
+        <v>49.85</v>
       </c>
       <c r="K17" t="n">
-        <v>14.19</v>
+        <v>52.99</v>
       </c>
       <c r="L17" t="n">
-        <v>-11.58</v>
+        <v>43.58</v>
       </c>
       <c r="M17" t="n">
-        <v>1977.02</v>
+        <v>4812.63</v>
       </c>
       <c r="N17" t="n">
-        <v>4187.65</v>
+        <v>6166.48</v>
       </c>
       <c r="O17" t="n">
-        <v>0.47</v>
+        <v>0.78</v>
       </c>
       <c r="P17" t="n">
-        <v>19.69</v>
+        <v>37</v>
       </c>
       <c r="Q17" t="n">
-        <v>19.73</v>
+        <v>37.8</v>
       </c>
       <c r="R17" t="n">
-        <v>18.68</v>
+        <v>35.87</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
@@ -1544,60 +1544,60 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>300017</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>深华发A</t>
+          <t>网宿科技</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14.82</v>
+        <v>16.55</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.2</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>15.72</v>
+        <v>17.05</v>
       </c>
       <c r="F18" t="n">
-        <v>17.03</v>
+        <v>17.19</v>
       </c>
       <c r="G18" t="n">
-        <v>17.02</v>
+        <v>17.87</v>
       </c>
       <c r="H18" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.228</v>
       </c>
       <c r="I18" t="n">
-        <v>0.547</v>
+        <v>-0.014</v>
       </c>
       <c r="J18" t="n">
-        <v>5.4</v>
+        <v>21.03</v>
       </c>
       <c r="K18" t="n">
-        <v>14.69</v>
+        <v>28.3</v>
       </c>
       <c r="L18" t="n">
-        <v>-13.17</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>1059.72</v>
+        <v>14819.21</v>
       </c>
       <c r="N18" t="n">
-        <v>1307.92</v>
+        <v>27077.87</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="P18" t="n">
-        <v>15.49</v>
+        <v>16.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.52</v>
+        <v>16.97</v>
       </c>
       <c r="R18" t="n">
-        <v>14.74</v>
+        <v>16.32</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
@@ -1608,60 +1608,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>603881</v>
+        <v>300418</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>数据港</t>
+          <t>昆仑万维</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>36.65</v>
+        <v>46.42</v>
       </c>
       <c r="D19" t="n">
-        <v>0.52</v>
+        <v>-2.87</v>
       </c>
       <c r="E19" t="n">
-        <v>37.7</v>
+        <v>48.86</v>
       </c>
       <c r="F19" t="n">
-        <v>37.31</v>
+        <v>49.54</v>
       </c>
       <c r="G19" t="n">
-        <v>37.45</v>
+        <v>51.09</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.06</v>
+        <v>-1.614</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.011</v>
+        <v>-1.282</v>
       </c>
       <c r="J19" t="n">
-        <v>49.85</v>
+        <v>20.39</v>
       </c>
       <c r="K19" t="n">
-        <v>52.99</v>
+        <v>28.18</v>
       </c>
       <c r="L19" t="n">
-        <v>43.58</v>
+        <v>4.8</v>
       </c>
       <c r="M19" t="n">
-        <v>4812.63</v>
+        <v>3783.22</v>
       </c>
       <c r="N19" t="n">
-        <v>6166.48</v>
+        <v>6480.28</v>
       </c>
       <c r="O19" t="n">
-        <v>0.78</v>
+        <v>0.58</v>
       </c>
       <c r="P19" t="n">
-        <v>37</v>
+        <v>47.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>37.8</v>
+        <v>48.09</v>
       </c>
       <c r="R19" t="n">
-        <v>35.87</v>
+        <v>46.13</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
@@ -1672,60 +1672,60 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>300017</v>
+        <v>2230</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>网宿科技</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.55</v>
+        <v>45.72</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="E20" t="n">
-        <v>17.05</v>
+        <v>46.24</v>
       </c>
       <c r="F20" t="n">
-        <v>17.19</v>
+        <v>46.54</v>
       </c>
       <c r="G20" t="n">
-        <v>17.87</v>
+        <v>49.22</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.228</v>
+        <v>-2.233</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.014</v>
+        <v>-2.099</v>
       </c>
       <c r="J20" t="n">
-        <v>21.03</v>
+        <v>17.16</v>
       </c>
       <c r="K20" t="n">
-        <v>28.3</v>
+        <v>17.38</v>
       </c>
       <c r="L20" t="n">
-        <v>6.5</v>
+        <v>16.71</v>
       </c>
       <c r="M20" t="n">
-        <v>14819.21</v>
+        <v>1869.61</v>
       </c>
       <c r="N20" t="n">
-        <v>27077.87</v>
+        <v>3229.13</v>
       </c>
       <c r="O20" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="P20" t="n">
-        <v>16.88</v>
+        <v>46.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.97</v>
+        <v>46.27</v>
       </c>
       <c r="R20" t="n">
-        <v>16.32</v>
+        <v>45.62</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
@@ -1736,60 +1736,60 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>300418</v>
+        <v>300058</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>昆仑万维</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>46.42</v>
+        <v>13.37</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.87</v>
+        <v>-3.54</v>
       </c>
       <c r="E21" t="n">
-        <v>48.86</v>
+        <v>14.2</v>
       </c>
       <c r="F21" t="n">
-        <v>49.54</v>
+        <v>14.13</v>
       </c>
       <c r="G21" t="n">
-        <v>51.09</v>
+        <v>14.87</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.614</v>
+        <v>-0.871</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.282</v>
+        <v>-0.87</v>
       </c>
       <c r="J21" t="n">
-        <v>20.39</v>
+        <v>28.01</v>
       </c>
       <c r="K21" t="n">
-        <v>28.18</v>
+        <v>34.61</v>
       </c>
       <c r="L21" t="n">
-        <v>4.8</v>
+        <v>14.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3783.22</v>
+        <v>21736.57</v>
       </c>
       <c r="N21" t="n">
-        <v>6480.28</v>
+        <v>26749.04</v>
       </c>
       <c r="O21" t="n">
-        <v>0.58</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>47.98</v>
+        <v>13.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>48.09</v>
+        <v>14.02</v>
       </c>
       <c r="R21" t="n">
-        <v>46.13</v>
+        <v>13.31</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
@@ -1800,60 +1800,60 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2230</v>
+        <v>300496</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>中科创达</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45.72</v>
+        <v>56.88</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.35</v>
+        <v>-1.23</v>
       </c>
       <c r="E22" t="n">
-        <v>46.24</v>
+        <v>58.23</v>
       </c>
       <c r="F22" t="n">
-        <v>46.54</v>
+        <v>59.19</v>
       </c>
       <c r="G22" t="n">
-        <v>49.22</v>
+        <v>63.31</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.233</v>
+        <v>-3.37</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.099</v>
+        <v>-3.025</v>
       </c>
       <c r="J22" t="n">
-        <v>17.16</v>
+        <v>10.36</v>
       </c>
       <c r="K22" t="n">
-        <v>17.38</v>
+        <v>13.33</v>
       </c>
       <c r="L22" t="n">
-        <v>16.71</v>
+        <v>4.4</v>
       </c>
       <c r="M22" t="n">
-        <v>1869.61</v>
+        <v>772.64</v>
       </c>
       <c r="N22" t="n">
-        <v>3229.13</v>
+        <v>1244.89</v>
       </c>
       <c r="O22" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="P22" t="n">
-        <v>46.02</v>
+        <v>59</v>
       </c>
       <c r="Q22" t="n">
-        <v>46.27</v>
+        <v>59</v>
       </c>
       <c r="R22" t="n">
-        <v>45.62</v>
+        <v>56.86</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
@@ -1864,60 +1864,60 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>300058</v>
+        <v>547</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>蓝色光标</t>
+          <t>航天发展</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13.37</v>
+        <v>25.78</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.54</v>
+        <v>-4.62</v>
       </c>
       <c r="E23" t="n">
-        <v>14.2</v>
+        <v>27.56</v>
       </c>
       <c r="F23" t="n">
-        <v>14.13</v>
+        <v>27.36</v>
       </c>
       <c r="G23" t="n">
-        <v>14.87</v>
+        <v>29.36</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.871</v>
+        <v>-0.88</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.87</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>28.01</v>
+        <v>36.97</v>
       </c>
       <c r="K23" t="n">
-        <v>34.61</v>
+        <v>40.19</v>
       </c>
       <c r="L23" t="n">
-        <v>14.8</v>
+        <v>30.53</v>
       </c>
       <c r="M23" t="n">
-        <v>21736.57</v>
+        <v>13262.66</v>
       </c>
       <c r="N23" t="n">
-        <v>26749.04</v>
+        <v>21745.33</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="P23" t="n">
-        <v>13.97</v>
+        <v>27.19</v>
       </c>
       <c r="Q23" t="n">
-        <v>14.02</v>
+        <v>27.3</v>
       </c>
       <c r="R23" t="n">
-        <v>13.31</v>
+        <v>25.7</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
@@ -1928,60 +1928,60 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>300496</v>
+        <v>2202</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中科创达</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>56.88</v>
+        <v>24.22</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.23</v>
+        <v>0.87</v>
       </c>
       <c r="E24" t="n">
-        <v>58.23</v>
+        <v>25.53</v>
       </c>
       <c r="F24" t="n">
-        <v>59.19</v>
+        <v>26.65</v>
       </c>
       <c r="G24" t="n">
-        <v>63.31</v>
+        <v>28.3</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.37</v>
+        <v>-0.67</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.025</v>
+        <v>-0.007</v>
       </c>
       <c r="J24" t="n">
-        <v>10.36</v>
+        <v>12.64</v>
       </c>
       <c r="K24" t="n">
-        <v>13.33</v>
+        <v>13.15</v>
       </c>
       <c r="L24" t="n">
-        <v>4.4</v>
+        <v>11.62</v>
       </c>
       <c r="M24" t="n">
-        <v>772.64</v>
+        <v>24211.4</v>
       </c>
       <c r="N24" t="n">
-        <v>1244.89</v>
+        <v>28234.59</v>
       </c>
       <c r="O24" t="n">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="P24" t="n">
-        <v>59</v>
+        <v>23.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>59</v>
+        <v>24.44</v>
       </c>
       <c r="R24" t="n">
-        <v>56.86</v>
+        <v>22.93</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
@@ -1992,60 +1992,60 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>547</v>
+        <v>301128</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>航天发展</t>
+          <t>强瑞技术</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.78</v>
+        <v>155</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.62</v>
+        <v>2.99</v>
       </c>
       <c r="E25" t="n">
-        <v>27.56</v>
+        <v>148.48</v>
       </c>
       <c r="F25" t="n">
-        <v>27.36</v>
+        <v>142.06</v>
       </c>
       <c r="G25" t="n">
-        <v>29.36</v>
+        <v>128.9</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.88</v>
+        <v>11.453</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5610000000000001</v>
+        <v>9.111000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>36.97</v>
+        <v>79.31</v>
       </c>
       <c r="K25" t="n">
-        <v>40.19</v>
+        <v>79.67</v>
       </c>
       <c r="L25" t="n">
-        <v>30.53</v>
+        <v>78.58</v>
       </c>
       <c r="M25" t="n">
-        <v>13262.66</v>
+        <v>710.4</v>
       </c>
       <c r="N25" t="n">
-        <v>21745.33</v>
+        <v>888.66</v>
       </c>
       <c r="O25" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="P25" t="n">
-        <v>27.19</v>
+        <v>155.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>27.3</v>
+        <v>164.1</v>
       </c>
       <c r="R25" t="n">
-        <v>25.7</v>
+        <v>150</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
@@ -2056,60 +2056,60 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2202</v>
+        <v>601899</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金风科技</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.22</v>
+        <v>32.91</v>
       </c>
       <c r="D26" t="n">
-        <v>0.87</v>
+        <v>-0.63</v>
       </c>
       <c r="E26" t="n">
-        <v>25.53</v>
+        <v>33.14</v>
       </c>
       <c r="F26" t="n">
-        <v>26.65</v>
+        <v>32.63</v>
       </c>
       <c r="G26" t="n">
-        <v>28.3</v>
+        <v>33.9</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.67</v>
+        <v>-1.168</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.007</v>
+        <v>-1.29</v>
       </c>
       <c r="J26" t="n">
-        <v>12.64</v>
+        <v>62.66</v>
       </c>
       <c r="K26" t="n">
-        <v>13.15</v>
+        <v>57.4</v>
       </c>
       <c r="L26" t="n">
-        <v>11.62</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>24211.4</v>
+        <v>14199.91</v>
       </c>
       <c r="N26" t="n">
-        <v>28234.59</v>
+        <v>30217.7</v>
       </c>
       <c r="O26" t="n">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
       <c r="P26" t="n">
-        <v>23.9</v>
+        <v>33.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>24.44</v>
+        <v>33.33</v>
       </c>
       <c r="R26" t="n">
-        <v>22.93</v>
+        <v>32.82</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
@@ -2120,60 +2120,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>301128</v>
+        <v>600219</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>强瑞技术</t>
+          <t>南山铝业</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>155</v>
+        <v>5.94</v>
       </c>
       <c r="D27" t="n">
-        <v>2.99</v>
+        <v>-3.88</v>
       </c>
       <c r="E27" t="n">
-        <v>148.48</v>
+        <v>6.18</v>
       </c>
       <c r="F27" t="n">
-        <v>142.06</v>
+        <v>6.05</v>
       </c>
       <c r="G27" t="n">
-        <v>128.9</v>
+        <v>6.51</v>
       </c>
       <c r="H27" t="n">
-        <v>11.453</v>
+        <v>-0.235</v>
       </c>
       <c r="I27" t="n">
-        <v>9.111000000000001</v>
+        <v>-0.196</v>
       </c>
       <c r="J27" t="n">
-        <v>79.31</v>
+        <v>41.76</v>
       </c>
       <c r="K27" t="n">
-        <v>79.67</v>
+        <v>39.1</v>
       </c>
       <c r="L27" t="n">
-        <v>78.58</v>
+        <v>47.08</v>
       </c>
       <c r="M27" t="n">
-        <v>710.4</v>
+        <v>19231.27</v>
       </c>
       <c r="N27" t="n">
-        <v>888.66</v>
+        <v>27894.36</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>155.03</v>
+        <v>6.17</v>
       </c>
       <c r="Q27" t="n">
-        <v>164.1</v>
+        <v>6.17</v>
       </c>
       <c r="R27" t="n">
-        <v>150</v>
+        <v>5.88</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
@@ -2184,60 +2184,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>601899</v>
+        <v>601939</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>建设银行</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32.91</v>
+        <v>9.4</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.63</v>
+        <v>-1.88</v>
       </c>
       <c r="E28" t="n">
-        <v>33.14</v>
+        <v>9.52</v>
       </c>
       <c r="F28" t="n">
-        <v>32.63</v>
+        <v>9.43</v>
       </c>
       <c r="G28" t="n">
-        <v>33.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.168</v>
+        <v>0.151</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.29</v>
+        <v>0.143</v>
       </c>
       <c r="J28" t="n">
-        <v>62.66</v>
+        <v>69.02</v>
       </c>
       <c r="K28" t="n">
-        <v>57.4</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>73.18000000000001</v>
+        <v>51.48</v>
       </c>
       <c r="M28" t="n">
-        <v>14199.91</v>
+        <v>8689.84</v>
       </c>
       <c r="N28" t="n">
-        <v>30217.7</v>
+        <v>10092.73</v>
       </c>
       <c r="O28" t="n">
-        <v>0.47</v>
+        <v>0.86</v>
       </c>
       <c r="P28" t="n">
-        <v>33.25</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="Q28" t="n">
-        <v>33.33</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="R28" t="n">
-        <v>32.82</v>
+        <v>9.33</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
@@ -2248,60 +2248,60 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>600219</v>
+        <v>600048</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南山铝业</t>
+          <t>保利发展</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5.94</v>
+        <v>5.51</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.88</v>
+        <v>-3.33</v>
       </c>
       <c r="E29" t="n">
-        <v>6.18</v>
+        <v>5.75</v>
       </c>
       <c r="F29" t="n">
-        <v>6.05</v>
+        <v>5.84</v>
       </c>
       <c r="G29" t="n">
-        <v>6.51</v>
+        <v>6.1</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.235</v>
+        <v>-0.241</v>
       </c>
       <c r="I29" t="n">
         <v>-0.196</v>
       </c>
       <c r="J29" t="n">
-        <v>41.76</v>
+        <v>7.81</v>
       </c>
       <c r="K29" t="n">
-        <v>39.1</v>
+        <v>10.09</v>
       </c>
       <c r="L29" t="n">
-        <v>47.08</v>
+        <v>3.27</v>
       </c>
       <c r="M29" t="n">
-        <v>19231.27</v>
+        <v>12363.64</v>
       </c>
       <c r="N29" t="n">
-        <v>27894.36</v>
+        <v>11406.08</v>
       </c>
       <c r="O29" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="P29" t="n">
-        <v>6.17</v>
+        <v>5.71</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.17</v>
+        <v>5.73</v>
       </c>
       <c r="R29" t="n">
-        <v>5.88</v>
+        <v>5.5</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
@@ -2312,60 +2312,60 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>601939</v>
+        <v>600941</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>建设银行</t>
+          <t>中国移动</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.4</v>
+        <v>93.02</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.88</v>
+        <v>-0.28</v>
       </c>
       <c r="E30" t="n">
-        <v>9.52</v>
+        <v>93.47</v>
       </c>
       <c r="F30" t="n">
-        <v>9.43</v>
+        <v>93.56</v>
       </c>
       <c r="G30" t="n">
-        <v>9.300000000000001</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.151</v>
+        <v>-0.712</v>
       </c>
       <c r="I30" t="n">
-        <v>0.143</v>
+        <v>-0.467</v>
       </c>
       <c r="J30" t="n">
-        <v>69.02</v>
+        <v>26.94</v>
       </c>
       <c r="K30" t="n">
-        <v>77.79000000000001</v>
+        <v>24.54</v>
       </c>
       <c r="L30" t="n">
-        <v>51.48</v>
+        <v>31.74</v>
       </c>
       <c r="M30" t="n">
-        <v>8689.84</v>
+        <v>707.17</v>
       </c>
       <c r="N30" t="n">
-        <v>10092.73</v>
+        <v>1028.52</v>
       </c>
       <c r="O30" t="n">
-        <v>0.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>9.529999999999999</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.550000000000001</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="R30" t="n">
-        <v>9.33</v>
+        <v>92.69</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
@@ -2376,60 +2376,60 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>600048</v>
+        <v>2352</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>保利发展</t>
+          <t>顺丰控股</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.51</v>
+        <v>37.61</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.33</v>
+        <v>-1.39</v>
       </c>
       <c r="E31" t="n">
-        <v>5.75</v>
+        <v>37.73</v>
       </c>
       <c r="F31" t="n">
-        <v>5.84</v>
+        <v>36.98</v>
       </c>
       <c r="G31" t="n">
-        <v>6.1</v>
+        <v>37.12</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.241</v>
+        <v>0.01</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.196</v>
+        <v>-0.188</v>
       </c>
       <c r="J31" t="n">
-        <v>7.81</v>
+        <v>73.42</v>
       </c>
       <c r="K31" t="n">
-        <v>10.09</v>
+        <v>67.06</v>
       </c>
       <c r="L31" t="n">
-        <v>3.27</v>
+        <v>86.12</v>
       </c>
       <c r="M31" t="n">
-        <v>12363.64</v>
+        <v>1525.58</v>
       </c>
       <c r="N31" t="n">
-        <v>11406.08</v>
+        <v>2290.44</v>
       </c>
       <c r="O31" t="n">
-        <v>1.08</v>
+        <v>0.67</v>
       </c>
       <c r="P31" t="n">
-        <v>5.71</v>
+        <v>38.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.73</v>
+        <v>38.26</v>
       </c>
       <c r="R31" t="n">
-        <v>5.5</v>
+        <v>37.55</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
@@ -2440,60 +2440,60 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>600941</v>
+        <v>603803</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中国移动</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>93.02</v>
+        <v>13.21</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="E32" t="n">
-        <v>93.47</v>
+        <v>13.22</v>
       </c>
       <c r="F32" t="n">
-        <v>93.56</v>
+        <v>14</v>
       </c>
       <c r="G32" t="n">
-        <v>95.26000000000001</v>
+        <v>13.23</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.712</v>
+        <v>0.635</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.467</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
-        <v>26.94</v>
+        <v>29.08</v>
       </c>
       <c r="K32" t="n">
-        <v>24.54</v>
+        <v>39.52</v>
       </c>
       <c r="L32" t="n">
-        <v>31.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>707.17</v>
+        <v>7801.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1028.52</v>
+        <v>8692.370000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="P32" t="n">
-        <v>93.29000000000001</v>
+        <v>13.57</v>
       </c>
       <c r="Q32" t="n">
-        <v>93.48999999999999</v>
+        <v>14.18</v>
       </c>
       <c r="R32" t="n">
-        <v>92.69</v>
+        <v>13</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
@@ -2504,60 +2504,60 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2352</v>
+        <v>2624</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>顺丰控股</t>
+          <t>完美世界</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37.61</v>
+        <v>19.21</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.39</v>
+        <v>-1.94</v>
       </c>
       <c r="E33" t="n">
-        <v>37.73</v>
+        <v>18.73</v>
       </c>
       <c r="F33" t="n">
-        <v>36.98</v>
+        <v>18.24</v>
       </c>
       <c r="G33" t="n">
-        <v>37.12</v>
+        <v>18.9</v>
       </c>
       <c r="H33" t="n">
-        <v>0.01</v>
+        <v>-0.23</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.188</v>
+        <v>-0.328</v>
       </c>
       <c r="J33" t="n">
-        <v>73.42</v>
+        <v>68.19</v>
       </c>
       <c r="K33" t="n">
-        <v>67.06</v>
+        <v>56.03</v>
       </c>
       <c r="L33" t="n">
-        <v>86.12</v>
+        <v>92.52</v>
       </c>
       <c r="M33" t="n">
-        <v>1525.58</v>
+        <v>5740.92</v>
       </c>
       <c r="N33" t="n">
-        <v>2290.44</v>
+        <v>5326.16</v>
       </c>
       <c r="O33" t="n">
-        <v>0.67</v>
+        <v>1.08</v>
       </c>
       <c r="P33" t="n">
-        <v>38.04</v>
+        <v>19.87</v>
       </c>
       <c r="Q33" t="n">
-        <v>38.26</v>
+        <v>19.9</v>
       </c>
       <c r="R33" t="n">
-        <v>37.55</v>
+        <v>19.01</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
@@ -2568,60 +2568,60 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>603803</v>
+        <v>2558</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t>巨人网络</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>13.21</v>
+        <v>33.2</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.38</v>
+        <v>-2.5</v>
       </c>
       <c r="E34" t="n">
-        <v>13.22</v>
+        <v>32.98</v>
       </c>
       <c r="F34" t="n">
-        <v>14</v>
+        <v>32.4</v>
       </c>
       <c r="G34" t="n">
-        <v>13.23</v>
+        <v>33.59</v>
       </c>
       <c r="H34" t="n">
-        <v>0.635</v>
+        <v>-1.516</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>-1.954</v>
       </c>
       <c r="J34" t="n">
-        <v>29.08</v>
+        <v>54.87</v>
       </c>
       <c r="K34" t="n">
-        <v>39.52</v>
+        <v>43.38</v>
       </c>
       <c r="L34" t="n">
-        <v>8.199999999999999</v>
+        <v>77.86</v>
       </c>
       <c r="M34" t="n">
-        <v>7801.1</v>
+        <v>3826.07</v>
       </c>
       <c r="N34" t="n">
-        <v>8692.370000000001</v>
+        <v>4267.9</v>
       </c>
       <c r="O34" t="n">
         <v>0.9</v>
       </c>
       <c r="P34" t="n">
-        <v>13.57</v>
+        <v>34.69</v>
       </c>
       <c r="Q34" t="n">
-        <v>14.18</v>
+        <v>34.75</v>
       </c>
       <c r="R34" t="n">
-        <v>13</v>
+        <v>33.07</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
@@ -2632,60 +2632,60 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2624</v>
+        <v>601088</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>完美世界</t>
+          <t>中国神华</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>19.21</v>
+        <v>47.58</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.94</v>
+        <v>-0.23</v>
       </c>
       <c r="E35" t="n">
-        <v>18.73</v>
+        <v>47.29</v>
       </c>
       <c r="F35" t="n">
-        <v>18.24</v>
+        <v>47.69</v>
       </c>
       <c r="G35" t="n">
-        <v>18.9</v>
+        <v>47.99</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.23</v>
+        <v>0.742</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.328</v>
+        <v>1.088</v>
       </c>
       <c r="J35" t="n">
-        <v>68.19</v>
+        <v>35.57</v>
       </c>
       <c r="K35" t="n">
-        <v>56.03</v>
+        <v>33.23</v>
       </c>
       <c r="L35" t="n">
-        <v>92.52</v>
+        <v>40.24</v>
       </c>
       <c r="M35" t="n">
-        <v>5740.92</v>
+        <v>2132.41</v>
       </c>
       <c r="N35" t="n">
-        <v>5326.16</v>
+        <v>4337.3</v>
       </c>
       <c r="O35" t="n">
-        <v>1.08</v>
+        <v>0.49</v>
       </c>
       <c r="P35" t="n">
-        <v>19.87</v>
+        <v>47.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>19.9</v>
+        <v>47.88</v>
       </c>
       <c r="R35" t="n">
-        <v>19.01</v>
+        <v>47.03</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
@@ -2696,60 +2696,60 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2558</v>
+        <v>600963</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>巨人网络</t>
+          <t>岳阳林纸</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>33.2</v>
+        <v>4.68</v>
       </c>
       <c r="D36" t="n">
-        <v>-2.5</v>
+        <v>-0.85</v>
       </c>
       <c r="E36" t="n">
-        <v>32.98</v>
+        <v>4.77</v>
       </c>
       <c r="F36" t="n">
-        <v>32.4</v>
+        <v>4.74</v>
       </c>
       <c r="G36" t="n">
-        <v>33.59</v>
+        <v>5.14</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.516</v>
+        <v>-0.251</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.954</v>
+        <v>-0.216</v>
       </c>
       <c r="J36" t="n">
-        <v>54.87</v>
+        <v>41.15</v>
       </c>
       <c r="K36" t="n">
-        <v>43.38</v>
+        <v>35.34</v>
       </c>
       <c r="L36" t="n">
-        <v>77.86</v>
+        <v>52.76</v>
       </c>
       <c r="M36" t="n">
-        <v>3826.07</v>
+        <v>2267.85</v>
       </c>
       <c r="N36" t="n">
-        <v>4267.9</v>
+        <v>4192.62</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9</v>
+        <v>0.54</v>
       </c>
       <c r="P36" t="n">
-        <v>34.69</v>
+        <v>4.73</v>
       </c>
       <c r="Q36" t="n">
-        <v>34.75</v>
+        <v>4.77</v>
       </c>
       <c r="R36" t="n">
-        <v>33.07</v>
+        <v>4.64</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
@@ -2760,60 +2760,60 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>601088</v>
+        <v>601877</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中国神华</t>
+          <t>正泰电器</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47.58</v>
+        <v>31.19</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.23</v>
+        <v>-1.76</v>
       </c>
       <c r="E37" t="n">
-        <v>47.29</v>
+        <v>32.34</v>
       </c>
       <c r="F37" t="n">
-        <v>47.69</v>
+        <v>33.5</v>
       </c>
       <c r="G37" t="n">
-        <v>47.99</v>
+        <v>35.51</v>
       </c>
       <c r="H37" t="n">
-        <v>0.742</v>
+        <v>-0.415</v>
       </c>
       <c r="I37" t="n">
-        <v>1.088</v>
+        <v>0.249</v>
       </c>
       <c r="J37" t="n">
-        <v>35.57</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>33.23</v>
+        <v>15.14</v>
       </c>
       <c r="L37" t="n">
-        <v>40.24</v>
+        <v>-0.95</v>
       </c>
       <c r="M37" t="n">
-        <v>2132.41</v>
+        <v>2060.09</v>
       </c>
       <c r="N37" t="n">
-        <v>4337.3</v>
+        <v>5484.54</v>
       </c>
       <c r="O37" t="n">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="P37" t="n">
-        <v>47.7</v>
+        <v>31.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>47.88</v>
+        <v>31.94</v>
       </c>
       <c r="R37" t="n">
-        <v>47.03</v>
+        <v>30.96</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
@@ -2824,60 +2824,60 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>600963</v>
+        <v>2049</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>岳阳林纸</t>
+          <t>紫光国微</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.68</v>
+        <v>64.92</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.85</v>
+        <v>-1.49</v>
       </c>
       <c r="E38" t="n">
-        <v>4.77</v>
+        <v>66.38</v>
       </c>
       <c r="F38" t="n">
-        <v>4.74</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>5.14</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.251</v>
+        <v>-2.991</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.216</v>
+        <v>-2.71</v>
       </c>
       <c r="J38" t="n">
-        <v>41.15</v>
+        <v>10.85</v>
       </c>
       <c r="K38" t="n">
-        <v>35.34</v>
+        <v>14.77</v>
       </c>
       <c r="L38" t="n">
-        <v>52.76</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>2267.85</v>
+        <v>887.3200000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>4192.62</v>
+        <v>1271.32</v>
       </c>
       <c r="O38" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="P38" t="n">
-        <v>4.73</v>
+        <v>66.22</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.77</v>
+        <v>66.38</v>
       </c>
       <c r="R38" t="n">
-        <v>4.64</v>
+        <v>64.8</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
@@ -2888,60 +2888,60 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>601877</v>
+        <v>601689</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>正泰电器</t>
+          <t>拓普集团</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>31.19</v>
+        <v>57.65</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.76</v>
+        <v>-1.72</v>
       </c>
       <c r="E39" t="n">
-        <v>32.34</v>
+        <v>57.84</v>
       </c>
       <c r="F39" t="n">
-        <v>33.5</v>
+        <v>57.71</v>
       </c>
       <c r="G39" t="n">
-        <v>35.51</v>
+        <v>60.06</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.415</v>
+        <v>-2.665</v>
       </c>
       <c r="I39" t="n">
-        <v>0.249</v>
+        <v>-2.951</v>
       </c>
       <c r="J39" t="n">
-        <v>9.779999999999999</v>
+        <v>48.56</v>
       </c>
       <c r="K39" t="n">
-        <v>15.14</v>
+        <v>40.8</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.95</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>2060.09</v>
+        <v>1625.78</v>
       </c>
       <c r="N39" t="n">
-        <v>5484.54</v>
+        <v>2247.79</v>
       </c>
       <c r="O39" t="n">
-        <v>0.38</v>
+        <v>0.72</v>
       </c>
       <c r="P39" t="n">
-        <v>31.75</v>
+        <v>59.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>31.94</v>
+        <v>59.29</v>
       </c>
       <c r="R39" t="n">
-        <v>30.96</v>
+        <v>57.33</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
@@ -2952,60 +2952,60 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>紫光国微</t>
+          <t>三花智控</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>64.92</v>
+        <v>41.9</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.49</v>
+        <v>-2.13</v>
       </c>
       <c r="E40" t="n">
-        <v>66.38</v>
+        <v>42.77</v>
       </c>
       <c r="F40" t="n">
-        <v>67.04000000000001</v>
+        <v>43.01</v>
       </c>
       <c r="G40" t="n">
-        <v>70.43000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.991</v>
+        <v>-1.893</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.71</v>
+        <v>-1.864</v>
       </c>
       <c r="J40" t="n">
-        <v>10.85</v>
+        <v>34.07</v>
       </c>
       <c r="K40" t="n">
-        <v>14.77</v>
+        <v>34.88</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>32.45</v>
       </c>
       <c r="M40" t="n">
-        <v>887.3200000000001</v>
+        <v>4568.37</v>
       </c>
       <c r="N40" t="n">
-        <v>1271.32</v>
+        <v>7288.17</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="P40" t="n">
-        <v>66.22</v>
+        <v>43</v>
       </c>
       <c r="Q40" t="n">
-        <v>66.38</v>
+        <v>43.42</v>
       </c>
       <c r="R40" t="n">
-        <v>64.8</v>
+        <v>41.88</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
@@ -3016,60 +3016,60 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>688271</v>
+        <v>887</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>联影医疗</t>
+          <t>中鼎股份</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>111.87</v>
+        <v>17.59</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.48</v>
+        <v>-1.46</v>
       </c>
       <c r="E41" t="n">
-        <v>113.23</v>
+        <v>17.97</v>
       </c>
       <c r="F41" t="n">
-        <v>113.03</v>
+        <v>17.95</v>
       </c>
       <c r="G41" t="n">
-        <v>116.25</v>
+        <v>18.6</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.36</v>
+        <v>-0.734</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.567</v>
+        <v>-0.761</v>
       </c>
       <c r="J41" t="n">
-        <v>47.37</v>
+        <v>41.44</v>
       </c>
       <c r="K41" t="n">
-        <v>39.88</v>
+        <v>40.15</v>
       </c>
       <c r="L41" t="n">
-        <v>62.35</v>
+        <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>305.87</v>
+        <v>916.3099999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>380.33</v>
+        <v>1735.63</v>
       </c>
       <c r="O41" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="P41" t="n">
-        <v>113.98</v>
+        <v>17.91</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.98</v>
+        <v>18</v>
       </c>
       <c r="R41" t="n">
-        <v>111.38</v>
+        <v>17.57</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
@@ -3080,60 +3080,60 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>688608</v>
+        <v>603236</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>恒玄科技</t>
+          <t>移远通信</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>161.9</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.66</v>
+        <v>1.6</v>
       </c>
       <c r="E42" t="n">
-        <v>169.15</v>
+        <v>73.47</v>
       </c>
       <c r="F42" t="n">
-        <v>165.4</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>172.21</v>
+        <v>76.31</v>
       </c>
       <c r="H42" t="n">
-        <v>-8.945</v>
+        <v>-3.109</v>
       </c>
       <c r="I42" t="n">
-        <v>-10.348</v>
+        <v>-3.342</v>
       </c>
       <c r="J42" t="n">
-        <v>42.2</v>
+        <v>37.82</v>
       </c>
       <c r="K42" t="n">
-        <v>43.33</v>
+        <v>31.01</v>
       </c>
       <c r="L42" t="n">
-        <v>39.94</v>
+        <v>51.44</v>
       </c>
       <c r="M42" t="n">
-        <v>254.57</v>
+        <v>520.21</v>
       </c>
       <c r="N42" t="n">
-        <v>306.73</v>
+        <v>499.08</v>
       </c>
       <c r="O42" t="n">
-        <v>0.83</v>
+        <v>1.04</v>
       </c>
       <c r="P42" t="n">
-        <v>167.75</v>
+        <v>72.33</v>
       </c>
       <c r="Q42" t="n">
-        <v>167.75</v>
+        <v>74.81</v>
       </c>
       <c r="R42" t="n">
-        <v>161.85</v>
+        <v>72</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
@@ -3144,60 +3144,60 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>688099</v>
+        <v>603072</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>晶晨股份</t>
+          <t>天和磁材</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>75.76000000000001</v>
+        <v>35.14</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.2</v>
+        <v>-1.68</v>
       </c>
       <c r="E43" t="n">
-        <v>78.47</v>
+        <v>35.82</v>
       </c>
       <c r="F43" t="n">
-        <v>79.79000000000001</v>
+        <v>35.63</v>
       </c>
       <c r="G43" t="n">
-        <v>84.61</v>
+        <v>37.65</v>
       </c>
       <c r="H43" t="n">
-        <v>-3.133</v>
+        <v>-1.698</v>
       </c>
       <c r="I43" t="n">
-        <v>-2.183</v>
+        <v>-1.663</v>
       </c>
       <c r="J43" t="n">
-        <v>11.53</v>
+        <v>45.89</v>
       </c>
       <c r="K43" t="n">
-        <v>17.4</v>
+        <v>39.7</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.2</v>
+        <v>58.28</v>
       </c>
       <c r="M43" t="n">
-        <v>667.0599999999999</v>
+        <v>139.61</v>
       </c>
       <c r="N43" t="n">
-        <v>1042.21</v>
+        <v>234.48</v>
       </c>
       <c r="O43" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="P43" t="n">
-        <v>76.81</v>
+        <v>35.74</v>
       </c>
       <c r="Q43" t="n">
-        <v>78.43000000000001</v>
+        <v>35.95</v>
       </c>
       <c r="R43" t="n">
-        <v>75.7</v>
+        <v>35</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
@@ -3208,60 +3208,60 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>688332</v>
+        <v>301023</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中科蓝讯</t>
+          <t>奕帆传动</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>118.96</v>
+        <v>37.1</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>-2.52</v>
       </c>
       <c r="E44" t="n">
-        <v>118.33</v>
+        <v>38.35</v>
       </c>
       <c r="F44" t="n">
-        <v>116.27</v>
+        <v>38.6</v>
       </c>
       <c r="G44" t="n">
-        <v>120.7</v>
+        <v>40.79</v>
       </c>
       <c r="H44" t="n">
-        <v>-3.856</v>
+        <v>-1.848</v>
       </c>
       <c r="I44" t="n">
-        <v>-4.536</v>
+        <v>-1.682</v>
       </c>
       <c r="J44" t="n">
-        <v>67.76000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="K44" t="n">
-        <v>51.98</v>
+        <v>21.12</v>
       </c>
       <c r="L44" t="n">
-        <v>99.31</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>117.24</v>
+        <v>93.61</v>
       </c>
       <c r="N44" t="n">
-        <v>129.17</v>
+        <v>126.36</v>
       </c>
       <c r="O44" t="n">
-        <v>0.91</v>
+        <v>0.74</v>
       </c>
       <c r="P44" t="n">
-        <v>119.5</v>
+        <v>38.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>120.5</v>
+        <v>38.45</v>
       </c>
       <c r="R44" t="n">
-        <v>118.2</v>
+        <v>37.02</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
@@ -3272,60 +3272,60 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>688049</v>
+        <v>2074</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>炬芯科技</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>43.63</v>
+        <v>33.46</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.11</v>
+        <v>-3.85</v>
       </c>
       <c r="E45" t="n">
-        <v>44.37</v>
+        <v>35.38</v>
       </c>
       <c r="F45" t="n">
-        <v>44.56</v>
+        <v>36.28</v>
       </c>
       <c r="G45" t="n">
-        <v>46.94</v>
+        <v>37.17</v>
       </c>
       <c r="H45" t="n">
-        <v>-2.146</v>
+        <v>-0.754</v>
       </c>
       <c r="I45" t="n">
-        <v>-2.072</v>
+        <v>-0.404</v>
       </c>
       <c r="J45" t="n">
-        <v>25.14</v>
+        <v>16.17</v>
       </c>
       <c r="K45" t="n">
-        <v>26.87</v>
+        <v>29.45</v>
       </c>
       <c r="L45" t="n">
-        <v>21.68</v>
+        <v>-10.39</v>
       </c>
       <c r="M45" t="n">
-        <v>241.16</v>
+        <v>3053.28</v>
       </c>
       <c r="N45" t="n">
-        <v>422.9</v>
+        <v>4395.15</v>
       </c>
       <c r="O45" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P45" t="n">
-        <v>43.97</v>
+        <v>34.73</v>
       </c>
       <c r="Q45" t="n">
-        <v>44.19</v>
+        <v>35.08</v>
       </c>
       <c r="R45" t="n">
-        <v>43.56</v>
+        <v>33.45</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
@@ -3336,60 +3336,60 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>601689</v>
+        <v>300450</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>拓普集团</t>
+          <t>先导智能</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>57.65</v>
+        <v>46.35</v>
       </c>
       <c r="D46" t="n">
-        <v>-1.72</v>
+        <v>-1.78</v>
       </c>
       <c r="E46" t="n">
-        <v>57.84</v>
+        <v>47.83</v>
       </c>
       <c r="F46" t="n">
-        <v>57.71</v>
+        <v>47.96</v>
       </c>
       <c r="G46" t="n">
-        <v>60.06</v>
+        <v>49.22</v>
       </c>
       <c r="H46" t="n">
-        <v>-2.665</v>
+        <v>-1.578</v>
       </c>
       <c r="I46" t="n">
-        <v>-2.951</v>
+        <v>-1.572</v>
       </c>
       <c r="J46" t="n">
-        <v>48.56</v>
+        <v>35.39</v>
       </c>
       <c r="K46" t="n">
-        <v>40.8</v>
+        <v>40.73</v>
       </c>
       <c r="L46" t="n">
-        <v>64.06999999999999</v>
+        <v>24.71</v>
       </c>
       <c r="M46" t="n">
-        <v>1625.78</v>
+        <v>2518.06</v>
       </c>
       <c r="N46" t="n">
-        <v>2247.79</v>
+        <v>4560.04</v>
       </c>
       <c r="O46" t="n">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
       <c r="P46" t="n">
-        <v>59.2</v>
+        <v>47.32</v>
       </c>
       <c r="Q46" t="n">
-        <v>59.29</v>
+        <v>47.66</v>
       </c>
       <c r="R46" t="n">
-        <v>57.33</v>
+        <v>46.27</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
@@ -3400,60 +3400,60 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2050</v>
+        <v>603200</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>三花智控</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>41.9</v>
+        <v>56.21</v>
       </c>
       <c r="D47" t="n">
-        <v>-2.13</v>
+        <v>-2.09</v>
       </c>
       <c r="E47" t="n">
-        <v>42.77</v>
+        <v>57.8</v>
       </c>
       <c r="F47" t="n">
-        <v>43.01</v>
+        <v>57.79</v>
       </c>
       <c r="G47" t="n">
-        <v>44.9</v>
+        <v>62.48</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.893</v>
+        <v>-4.757</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.864</v>
+        <v>-4.806</v>
       </c>
       <c r="J47" t="n">
-        <v>34.07</v>
+        <v>31.53</v>
       </c>
       <c r="K47" t="n">
-        <v>34.88</v>
+        <v>29.17</v>
       </c>
       <c r="L47" t="n">
-        <v>32.45</v>
+        <v>36.25</v>
       </c>
       <c r="M47" t="n">
-        <v>4568.37</v>
+        <v>289.85</v>
       </c>
       <c r="N47" t="n">
-        <v>7288.17</v>
+        <v>500.34</v>
       </c>
       <c r="O47" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="P47" t="n">
-        <v>43</v>
+        <v>57.41</v>
       </c>
       <c r="Q47" t="n">
-        <v>43.42</v>
+        <v>58.5</v>
       </c>
       <c r="R47" t="n">
-        <v>41.88</v>
+        <v>56.21</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
@@ -3464,60 +3464,60 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>887</v>
+        <v>300409</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中鼎股份</t>
+          <t>道氏技术</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>17.59</v>
+        <v>24.02</v>
       </c>
       <c r="D48" t="n">
-        <v>-1.46</v>
+        <v>-1.92</v>
       </c>
       <c r="E48" t="n">
-        <v>17.97</v>
+        <v>24.72</v>
       </c>
       <c r="F48" t="n">
-        <v>17.95</v>
+        <v>24.72</v>
       </c>
       <c r="G48" t="n">
-        <v>18.6</v>
+        <v>26.51</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.734</v>
+        <v>-1.127</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.761</v>
+        <v>-0.969</v>
       </c>
       <c r="J48" t="n">
-        <v>41.44</v>
+        <v>25.6</v>
       </c>
       <c r="K48" t="n">
-        <v>40.15</v>
+        <v>26.1</v>
       </c>
       <c r="L48" t="n">
-        <v>44</v>
+        <v>24.61</v>
       </c>
       <c r="M48" t="n">
-        <v>916.3099999999999</v>
+        <v>1262.04</v>
       </c>
       <c r="N48" t="n">
-        <v>1735.63</v>
+        <v>3605.02</v>
       </c>
       <c r="O48" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="P48" t="n">
-        <v>17.91</v>
+        <v>24.58</v>
       </c>
       <c r="Q48" t="n">
-        <v>18</v>
+        <v>24.74</v>
       </c>
       <c r="R48" t="n">
-        <v>17.57</v>
+        <v>24.01</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
@@ -3528,60 +3528,60 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>603236</v>
+        <v>2202</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>73.48999999999999</v>
+        <v>24.22</v>
       </c>
       <c r="D49" t="n">
-        <v>1.6</v>
+        <v>0.87</v>
       </c>
       <c r="E49" t="n">
-        <v>73.47</v>
+        <v>25.53</v>
       </c>
       <c r="F49" t="n">
-        <v>73.43000000000001</v>
+        <v>26.65</v>
       </c>
       <c r="G49" t="n">
-        <v>76.31</v>
+        <v>28.3</v>
       </c>
       <c r="H49" t="n">
-        <v>-3.109</v>
+        <v>-0.67</v>
       </c>
       <c r="I49" t="n">
-        <v>-3.342</v>
+        <v>-0.007</v>
       </c>
       <c r="J49" t="n">
-        <v>37.82</v>
+        <v>12.64</v>
       </c>
       <c r="K49" t="n">
-        <v>31.01</v>
+        <v>13.15</v>
       </c>
       <c r="L49" t="n">
-        <v>51.44</v>
+        <v>11.62</v>
       </c>
       <c r="M49" t="n">
-        <v>520.21</v>
+        <v>24211.4</v>
       </c>
       <c r="N49" t="n">
-        <v>499.08</v>
+        <v>28234.59</v>
       </c>
       <c r="O49" t="n">
-        <v>1.04</v>
+        <v>0.86</v>
       </c>
       <c r="P49" t="n">
-        <v>72.33</v>
+        <v>23.9</v>
       </c>
       <c r="Q49" t="n">
-        <v>74.81</v>
+        <v>24.44</v>
       </c>
       <c r="R49" t="n">
-        <v>72</v>
+        <v>22.93</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
@@ -3592,60 +3592,60 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>603072</v>
+        <v>600990</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>天和磁材</t>
+          <t>四创电子</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>35.14</v>
+        <v>21.65</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.68</v>
+        <v>-2.61</v>
       </c>
       <c r="E50" t="n">
-        <v>35.82</v>
+        <v>22.44</v>
       </c>
       <c r="F50" t="n">
-        <v>35.63</v>
+        <v>22.45</v>
       </c>
       <c r="G50" t="n">
-        <v>37.65</v>
+        <v>23.78</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.698</v>
+        <v>-1.238</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.663</v>
+        <v>-1.21</v>
       </c>
       <c r="J50" t="n">
-        <v>45.89</v>
+        <v>20.72</v>
       </c>
       <c r="K50" t="n">
-        <v>39.7</v>
+        <v>24.46</v>
       </c>
       <c r="L50" t="n">
-        <v>58.28</v>
+        <v>13.24</v>
       </c>
       <c r="M50" t="n">
-        <v>139.61</v>
+        <v>322.53</v>
       </c>
       <c r="N50" t="n">
-        <v>234.48</v>
+        <v>416.36</v>
       </c>
       <c r="O50" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="P50" t="n">
-        <v>35.74</v>
+        <v>22.23</v>
       </c>
       <c r="Q50" t="n">
-        <v>35.95</v>
+        <v>22.34</v>
       </c>
       <c r="R50" t="n">
-        <v>35</v>
+        <v>21.56</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
@@ -3656,60 +3656,60 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>301023</v>
+        <v>2025</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>奕帆传动</t>
+          <t>航天电器</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37.1</v>
+        <v>60.65</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.52</v>
+        <v>0.05</v>
       </c>
       <c r="E51" t="n">
-        <v>38.35</v>
+        <v>63.2</v>
       </c>
       <c r="F51" t="n">
-        <v>38.6</v>
+        <v>63.67</v>
       </c>
       <c r="G51" t="n">
-        <v>40.79</v>
+        <v>60.64</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.848</v>
+        <v>2.365</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.682</v>
+        <v>2.654</v>
       </c>
       <c r="J51" t="n">
-        <v>16.9</v>
+        <v>40.32</v>
       </c>
       <c r="K51" t="n">
-        <v>21.12</v>
+        <v>53.83</v>
       </c>
       <c r="L51" t="n">
-        <v>8.470000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="M51" t="n">
-        <v>93.61</v>
+        <v>2381.43</v>
       </c>
       <c r="N51" t="n">
-        <v>126.36</v>
+        <v>3609.08</v>
       </c>
       <c r="O51" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="P51" t="n">
-        <v>38.2</v>
+        <v>60.62</v>
       </c>
       <c r="Q51" t="n">
-        <v>38.45</v>
+        <v>62.83</v>
       </c>
       <c r="R51" t="n">
-        <v>37.02</v>
+        <v>58.7</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
@@ -3720,60 +3720,60 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2074</v>
+        <v>600584</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>33.46</v>
+        <v>38.29</v>
       </c>
       <c r="D52" t="n">
-        <v>-3.85</v>
+        <v>-0.49</v>
       </c>
       <c r="E52" t="n">
-        <v>35.38</v>
+        <v>38.97</v>
       </c>
       <c r="F52" t="n">
-        <v>36.28</v>
+        <v>39.3</v>
       </c>
       <c r="G52" t="n">
-        <v>37.17</v>
+        <v>42.17</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.754</v>
+        <v>-1.96</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.404</v>
+        <v>-1.593</v>
       </c>
       <c r="J52" t="n">
-        <v>16.17</v>
+        <v>10.7</v>
       </c>
       <c r="K52" t="n">
-        <v>29.45</v>
+        <v>13.23</v>
       </c>
       <c r="L52" t="n">
-        <v>-10.39</v>
+        <v>5.65</v>
       </c>
       <c r="M52" t="n">
-        <v>3053.28</v>
+        <v>2617.06</v>
       </c>
       <c r="N52" t="n">
-        <v>4395.15</v>
+        <v>5761.89</v>
       </c>
       <c r="O52" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="P52" t="n">
-        <v>34.73</v>
+        <v>38.88</v>
       </c>
       <c r="Q52" t="n">
-        <v>35.08</v>
+        <v>38.98</v>
       </c>
       <c r="R52" t="n">
-        <v>33.45</v>
+        <v>38.02</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
@@ -3784,60 +3784,60 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>300450</v>
+        <v>300759</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>先导智能</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>46.35</v>
+        <v>30.07</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.78</v>
+        <v>-1.8</v>
       </c>
       <c r="E53" t="n">
-        <v>47.83</v>
+        <v>29.16</v>
       </c>
       <c r="F53" t="n">
-        <v>47.96</v>
+        <v>27.49</v>
       </c>
       <c r="G53" t="n">
-        <v>49.22</v>
+        <v>27.46</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.578</v>
+        <v>0.153</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.572</v>
+        <v>-0.416</v>
       </c>
       <c r="J53" t="n">
-        <v>35.39</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>40.73</v>
+        <v>63.86</v>
       </c>
       <c r="L53" t="n">
-        <v>24.71</v>
+        <v>108.74</v>
       </c>
       <c r="M53" t="n">
-        <v>2518.06</v>
+        <v>4109.71</v>
       </c>
       <c r="N53" t="n">
-        <v>4560.04</v>
+        <v>3006.3</v>
       </c>
       <c r="O53" t="n">
-        <v>0.55</v>
+        <v>1.37</v>
       </c>
       <c r="P53" t="n">
-        <v>47.32</v>
+        <v>30.39</v>
       </c>
       <c r="Q53" t="n">
-        <v>47.66</v>
+        <v>30.59</v>
       </c>
       <c r="R53" t="n">
-        <v>46.27</v>
+        <v>29.82</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr">
@@ -3848,60 +3848,60 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>688778</v>
+        <v>301333</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>诺思格</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>69.16</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>-2.04</v>
+        <v>-5.14</v>
       </c>
       <c r="E54" t="n">
-        <v>71.73999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="F54" t="n">
-        <v>72.02</v>
+        <v>63.27</v>
       </c>
       <c r="G54" t="n">
-        <v>73.66</v>
+        <v>63.26</v>
       </c>
       <c r="H54" t="n">
-        <v>-2.47</v>
+        <v>-0.417</v>
       </c>
       <c r="I54" t="n">
-        <v>-2.484</v>
+        <v>-1.724</v>
       </c>
       <c r="J54" t="n">
-        <v>45.76</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>51.6</v>
+        <v>66.17</v>
       </c>
       <c r="L54" t="n">
-        <v>34.07</v>
+        <v>80.69</v>
       </c>
       <c r="M54" t="n">
-        <v>309.14</v>
+        <v>287.12</v>
       </c>
       <c r="N54" t="n">
-        <v>536.33</v>
+        <v>229.26</v>
       </c>
       <c r="O54" t="n">
-        <v>0.58</v>
+        <v>1.25</v>
       </c>
       <c r="P54" t="n">
-        <v>70.8</v>
+        <v>66.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>71.48</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="R54" t="n">
-        <v>68.8</v>
+        <v>65.41</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
@@ -3912,60 +3912,60 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>688116</v>
+        <v>963</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>天奈科技</t>
+          <t>华东医药</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>36.9</v>
+        <v>36.29</v>
       </c>
       <c r="D55" t="n">
-        <v>-2.77</v>
+        <v>-1.6</v>
       </c>
       <c r="E55" t="n">
-        <v>39.03</v>
+        <v>36.08</v>
       </c>
       <c r="F55" t="n">
-        <v>39.82</v>
+        <v>35.1</v>
       </c>
       <c r="G55" t="n">
-        <v>41.36</v>
+        <v>35.22</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.742</v>
+        <v>0.037</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.49</v>
+        <v>-0.264</v>
       </c>
       <c r="J55" t="n">
-        <v>18.01</v>
+        <v>78.05</v>
       </c>
       <c r="K55" t="n">
-        <v>26.63</v>
+        <v>67.72</v>
       </c>
       <c r="L55" t="n">
-        <v>0.79</v>
+        <v>98.69</v>
       </c>
       <c r="M55" t="n">
-        <v>572.42</v>
+        <v>1153.73</v>
       </c>
       <c r="N55" t="n">
-        <v>779.28</v>
+        <v>1076.56</v>
       </c>
       <c r="O55" t="n">
-        <v>0.73</v>
+        <v>1.07</v>
       </c>
       <c r="P55" t="n">
-        <v>38</v>
+        <v>36.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>38.47</v>
+        <v>36.6</v>
       </c>
       <c r="R55" t="n">
-        <v>36.82</v>
+        <v>36.04</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
@@ -3976,60 +3976,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>603200</v>
+        <v>603658</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>安图生物</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>56.21</v>
+        <v>33.98</v>
       </c>
       <c r="D56" t="n">
-        <v>-2.09</v>
+        <v>-1.48</v>
       </c>
       <c r="E56" t="n">
-        <v>57.8</v>
+        <v>33.96</v>
       </c>
       <c r="F56" t="n">
-        <v>57.79</v>
+        <v>33.51</v>
       </c>
       <c r="G56" t="n">
-        <v>62.48</v>
+        <v>34.18</v>
       </c>
       <c r="H56" t="n">
-        <v>-4.757</v>
+        <v>-0.479</v>
       </c>
       <c r="I56" t="n">
-        <v>-4.806</v>
+        <v>-0.603</v>
       </c>
       <c r="J56" t="n">
-        <v>31.53</v>
+        <v>64.03</v>
       </c>
       <c r="K56" t="n">
-        <v>29.17</v>
+        <v>49.79</v>
       </c>
       <c r="L56" t="n">
-        <v>36.25</v>
+        <v>92.52</v>
       </c>
       <c r="M56" t="n">
-        <v>289.85</v>
+        <v>194.17</v>
       </c>
       <c r="N56" t="n">
-        <v>500.34</v>
+        <v>193.2</v>
       </c>
       <c r="O56" t="n">
-        <v>0.58</v>
+        <v>1.01</v>
       </c>
       <c r="P56" t="n">
-        <v>57.41</v>
+        <v>34.28</v>
       </c>
       <c r="Q56" t="n">
-        <v>58.5</v>
+        <v>34.45</v>
       </c>
       <c r="R56" t="n">
-        <v>56.21</v>
+        <v>33.73</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
@@ -4040,895 +4040,63 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>300409</v>
+        <v>300357</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>道氏技术</t>
+          <t>我武生物</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>24.02</v>
+        <v>25.53</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.92</v>
+        <v>-3.44</v>
       </c>
       <c r="E57" t="n">
-        <v>24.72</v>
+        <v>25.97</v>
       </c>
       <c r="F57" t="n">
-        <v>24.72</v>
+        <v>25.05</v>
       </c>
       <c r="G57" t="n">
-        <v>26.51</v>
+        <v>25.05</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.127</v>
+        <v>-0.186</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.969</v>
+        <v>-0.486</v>
       </c>
       <c r="J57" t="n">
-        <v>25.6</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>26.1</v>
+        <v>66.77</v>
       </c>
       <c r="L57" t="n">
-        <v>24.61</v>
+        <v>88.42</v>
       </c>
       <c r="M57" t="n">
-        <v>1262.04</v>
+        <v>1057.86</v>
       </c>
       <c r="N57" t="n">
-        <v>3605.02</v>
+        <v>1143.81</v>
       </c>
       <c r="O57" t="n">
-        <v>0.35</v>
+        <v>0.92</v>
       </c>
       <c r="P57" t="n">
-        <v>24.58</v>
+        <v>26.07</v>
       </c>
       <c r="Q57" t="n">
-        <v>24.74</v>
+        <v>26.28</v>
       </c>
       <c r="R57" t="n">
-        <v>24.01</v>
+        <v>25.49</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>2202</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>金风科技</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>24.22</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E58" t="n">
-        <v>25.53</v>
-      </c>
-      <c r="F58" t="n">
-        <v>26.65</v>
-      </c>
-      <c r="G58" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="J58" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="K58" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="L58" t="n">
-        <v>11.62</v>
-      </c>
-      <c r="M58" t="n">
-        <v>24211.4</v>
-      </c>
-      <c r="N58" t="n">
-        <v>28234.59</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P58" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="R58" t="n">
-        <v>22.93</v>
-      </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>688066</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>航天宏图</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>17</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-6.44</v>
-      </c>
-      <c r="E59" t="n">
-        <v>18.82</v>
-      </c>
-      <c r="F59" t="n">
-        <v>19.47</v>
-      </c>
-      <c r="G59" t="n">
-        <v>21.13</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-2.121</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-2.019</v>
-      </c>
-      <c r="J59" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="K59" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="L59" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1167.25</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1032.33</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P59" t="n">
-        <v>18.22</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="R59" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>600990</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>四创电子</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-2.61</v>
-      </c>
-      <c r="E60" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="F60" t="n">
-        <v>22.45</v>
-      </c>
-      <c r="G60" t="n">
-        <v>23.78</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-1.238</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-1.21</v>
-      </c>
-      <c r="J60" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="K60" t="n">
-        <v>24.46</v>
-      </c>
-      <c r="L60" t="n">
-        <v>13.24</v>
-      </c>
-      <c r="M60" t="n">
-        <v>322.53</v>
-      </c>
-      <c r="N60" t="n">
-        <v>416.36</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="P60" t="n">
-        <v>22.23</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>22.34</v>
-      </c>
-      <c r="R60" t="n">
-        <v>21.56</v>
-      </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>航天电器</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E61" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="F61" t="n">
-        <v>63.67</v>
-      </c>
-      <c r="G61" t="n">
-        <v>60.64</v>
-      </c>
-      <c r="H61" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2.654</v>
-      </c>
-      <c r="J61" t="n">
-        <v>40.32</v>
-      </c>
-      <c r="K61" t="n">
-        <v>53.83</v>
-      </c>
-      <c r="L61" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="M61" t="n">
-        <v>2381.43</v>
-      </c>
-      <c r="N61" t="n">
-        <v>3609.08</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="P61" t="n">
-        <v>60.62</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>62.83</v>
-      </c>
-      <c r="R61" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>600584</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>长电科技</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>38.29</v>
-      </c>
-      <c r="D62" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="E62" t="n">
-        <v>38.97</v>
-      </c>
-      <c r="F62" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="G62" t="n">
-        <v>42.17</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="I62" t="n">
-        <v>-1.593</v>
-      </c>
-      <c r="J62" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="K62" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="L62" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="M62" t="n">
-        <v>2617.06</v>
-      </c>
-      <c r="N62" t="n">
-        <v>5761.89</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P62" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>38.98</v>
-      </c>
-      <c r="R62" t="n">
-        <v>38.02</v>
-      </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>688295</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>中复神鹰</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>50.01</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="E63" t="n">
-        <v>53.69</v>
-      </c>
-      <c r="F63" t="n">
-        <v>56.69</v>
-      </c>
-      <c r="G63" t="n">
-        <v>51.84</v>
-      </c>
-      <c r="H63" t="n">
-        <v>4.683</v>
-      </c>
-      <c r="I63" t="n">
-        <v>5.954</v>
-      </c>
-      <c r="J63" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="K63" t="n">
-        <v>34.59</v>
-      </c>
-      <c r="L63" t="n">
-        <v>-20.24</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1933.17</v>
-      </c>
-      <c r="N63" t="n">
-        <v>2814.68</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="P63" t="n">
-        <v>52.38</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>52.66</v>
-      </c>
-      <c r="R63" t="n">
-        <v>50</v>
-      </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>300759</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>康龙化成</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>30.07</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="E64" t="n">
-        <v>29.16</v>
-      </c>
-      <c r="F64" t="n">
-        <v>27.49</v>
-      </c>
-      <c r="G64" t="n">
-        <v>27.46</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="I64" t="n">
-        <v>-0.416</v>
-      </c>
-      <c r="J64" t="n">
-        <v>78.81999999999999</v>
-      </c>
-      <c r="K64" t="n">
-        <v>63.86</v>
-      </c>
-      <c r="L64" t="n">
-        <v>108.74</v>
-      </c>
-      <c r="M64" t="n">
-        <v>4109.71</v>
-      </c>
-      <c r="N64" t="n">
-        <v>3006.3</v>
-      </c>
-      <c r="O64" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P64" t="n">
-        <v>30.39</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="R64" t="n">
-        <v>29.82</v>
-      </c>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>688621</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>阳光诺和</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>65.56999999999999</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="E65" t="n">
-        <v>66.33</v>
-      </c>
-      <c r="F65" t="n">
-        <v>63.53</v>
-      </c>
-      <c r="G65" t="n">
-        <v>63.03</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="I65" t="n">
-        <v>-0.494</v>
-      </c>
-      <c r="J65" t="n">
-        <v>77.61</v>
-      </c>
-      <c r="K65" t="n">
-        <v>72.14</v>
-      </c>
-      <c r="L65" t="n">
-        <v>88.56</v>
-      </c>
-      <c r="M65" t="n">
-        <v>303.1</v>
-      </c>
-      <c r="N65" t="n">
-        <v>219.18</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P65" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>68</v>
-      </c>
-      <c r="R65" t="n">
-        <v>65</v>
-      </c>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>301333</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>诺思格</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="D66" t="n">
-        <v>-5.14</v>
-      </c>
-      <c r="E66" t="n">
-        <v>67.86</v>
-      </c>
-      <c r="F66" t="n">
-        <v>63.27</v>
-      </c>
-      <c r="G66" t="n">
-        <v>63.26</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-0.417</v>
-      </c>
-      <c r="I66" t="n">
-        <v>-1.724</v>
-      </c>
-      <c r="J66" t="n">
-        <v>71.01000000000001</v>
-      </c>
-      <c r="K66" t="n">
-        <v>66.17</v>
-      </c>
-      <c r="L66" t="n">
-        <v>80.69</v>
-      </c>
-      <c r="M66" t="n">
-        <v>287.12</v>
-      </c>
-      <c r="N66" t="n">
-        <v>229.26</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P66" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="R66" t="n">
-        <v>65.41</v>
-      </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>963</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>华东医药</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>36.29</v>
-      </c>
-      <c r="D67" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="E67" t="n">
-        <v>36.08</v>
-      </c>
-      <c r="F67" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>35.22</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="I67" t="n">
-        <v>-0.264</v>
-      </c>
-      <c r="J67" t="n">
-        <v>78.05</v>
-      </c>
-      <c r="K67" t="n">
-        <v>67.72</v>
-      </c>
-      <c r="L67" t="n">
-        <v>98.69</v>
-      </c>
-      <c r="M67" t="n">
-        <v>1153.73</v>
-      </c>
-      <c r="N67" t="n">
-        <v>1076.56</v>
-      </c>
-      <c r="O67" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P67" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="R67" t="n">
-        <v>36.04</v>
-      </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>603658</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>安图生物</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>33.98</v>
-      </c>
-      <c r="D68" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="E68" t="n">
-        <v>33.96</v>
-      </c>
-      <c r="F68" t="n">
-        <v>33.51</v>
-      </c>
-      <c r="G68" t="n">
-        <v>34.18</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-0.479</v>
-      </c>
-      <c r="I68" t="n">
-        <v>-0.603</v>
-      </c>
-      <c r="J68" t="n">
-        <v>64.03</v>
-      </c>
-      <c r="K68" t="n">
-        <v>49.79</v>
-      </c>
-      <c r="L68" t="n">
-        <v>92.52</v>
-      </c>
-      <c r="M68" t="n">
-        <v>194.17</v>
-      </c>
-      <c r="N68" t="n">
-        <v>193.2</v>
-      </c>
-      <c r="O68" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P68" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="R68" t="n">
-        <v>33.73</v>
-      </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>300357</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>我武生物</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>25.53</v>
-      </c>
-      <c r="D69" t="n">
-        <v>-3.44</v>
-      </c>
-      <c r="E69" t="n">
-        <v>25.97</v>
-      </c>
-      <c r="F69" t="n">
-        <v>25.05</v>
-      </c>
-      <c r="G69" t="n">
-        <v>25.05</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-0.186</v>
-      </c>
-      <c r="I69" t="n">
-        <v>-0.486</v>
-      </c>
-      <c r="J69" t="n">
-        <v>73.98999999999999</v>
-      </c>
-      <c r="K69" t="n">
-        <v>66.77</v>
-      </c>
-      <c r="L69" t="n">
-        <v>88.42</v>
-      </c>
-      <c r="M69" t="n">
-        <v>1057.86</v>
-      </c>
-      <c r="N69" t="n">
-        <v>1143.81</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="P69" t="n">
-        <v>26.07</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>26.28</v>
-      </c>
-      <c r="R69" t="n">
-        <v>25.49</v>
-      </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>688050</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>爱博医疗</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="D70" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="E70" t="n">
-        <v>51.72</v>
-      </c>
-      <c r="F70" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="G70" t="n">
-        <v>53.05</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="I70" t="n">
-        <v>-2.032</v>
-      </c>
-      <c r="J70" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="K70" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="L70" t="n">
-        <v>66.83</v>
-      </c>
-      <c r="M70" t="n">
-        <v>102.26</v>
-      </c>
-      <c r="N70" t="n">
-        <v>178.13</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="P70" t="n">
-        <v>51.55</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="R70" t="n">
-        <v>50.72</v>
-      </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
